--- a/reports/policy-tracker.xlsx
+++ b/reports/policy-tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3171" uniqueCount="1357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3571" uniqueCount="1519">
   <si>
     <t>Run #</t>
   </si>
@@ -4082,6 +4082,492 @@
   </si>
   <si>
     <t>04/08/2026, 19:42:02</t>
+  </si>
+  <si>
+    <t>DA-MLI-068875216</t>
+  </si>
+  <si>
+    <t>04/08/2026, 19:59:17</t>
+  </si>
+  <si>
+    <t>DA-MLI-069001217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 14:22:17</t>
+  </si>
+  <si>
+    <t>CP-NI-069004217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 14:55:21</t>
+  </si>
+  <si>
+    <t>CP-NI-069005217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 14:57:05</t>
+  </si>
+  <si>
+    <t>CP-SC-069006217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 14:58:28</t>
+  </si>
+  <si>
+    <t>DA-MLI-069007217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:00:53</t>
+  </si>
+  <si>
+    <t>DA-MLI-069008217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:05:58</t>
+  </si>
+  <si>
+    <t>DA-MLI-069009217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:09:01</t>
+  </si>
+  <si>
+    <t>DA-MLI-069010217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:11:20</t>
+  </si>
+  <si>
+    <t>DA-MLI-069011217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:13:37</t>
+  </si>
+  <si>
+    <t>DA-MLI-069012217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:16:09</t>
+  </si>
+  <si>
+    <t>DA-MLI-069013217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:18:27</t>
+  </si>
+  <si>
+    <t>DA-MLI-069014217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:19:56</t>
+  </si>
+  <si>
+    <t>DA-MLI-069016217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:22:17</t>
+  </si>
+  <si>
+    <t>DA-MLI-069017217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:24:40</t>
+  </si>
+  <si>
+    <t>DA-MLI-069018217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:27:06</t>
+  </si>
+  <si>
+    <t>DA-MLI-069019217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:29:33</t>
+  </si>
+  <si>
+    <t>DA-MLI-069020217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:32:14</t>
+  </si>
+  <si>
+    <t>DA-MLI-069021217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:34:36</t>
+  </si>
+  <si>
+    <t>DA-MLI-069022217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:36:58</t>
+  </si>
+  <si>
+    <t>DA-MLI-069023217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:39:18</t>
+  </si>
+  <si>
+    <t>DA-MLI-069024217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:41:55</t>
+  </si>
+  <si>
+    <t>DA-MLI-069025217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:44:12</t>
+  </si>
+  <si>
+    <t>DA-MLI-069026217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:45:53</t>
+  </si>
+  <si>
+    <t>DA-MLI-069027217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:48:14</t>
+  </si>
+  <si>
+    <t>DA-MLI-069028217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:50:40</t>
+  </si>
+  <si>
+    <t>DA-MLI-069029217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:53:11</t>
+  </si>
+  <si>
+    <t>DA-MLI-069030217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 15:58:12</t>
+  </si>
+  <si>
+    <t>CP-MLI-069031217</t>
+  </si>
+  <si>
+    <t>TC_REG_034_COMM | Create Claim on a live commercial policy and submit mandatory details</t>
+  </si>
+  <si>
+    <t>05/08/2026, 16:02:33</t>
+  </si>
+  <si>
+    <t>CP-MLI-069033217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 16:23:16</t>
+  </si>
+  <si>
+    <t>CP-MLI-069035217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 16:27:49</t>
+  </si>
+  <si>
+    <t>CP-MLI-069036217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 16:30:24</t>
+  </si>
+  <si>
+    <t>CP-MLI-069037217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 16:32:50</t>
+  </si>
+  <si>
+    <t>CP-MLI-069038217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 16:35:19</t>
+  </si>
+  <si>
+    <t>CP-MLI-069039217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 16:37:44</t>
+  </si>
+  <si>
+    <t>CP-MLI-069041217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 16:40:17</t>
+  </si>
+  <si>
+    <t>CP-MLI-069043217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 16:42:36</t>
+  </si>
+  <si>
+    <t>CP-MLI-069044217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 16:45:07</t>
+  </si>
+  <si>
+    <t>CP-MLI-069045217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 16:47:37</t>
+  </si>
+  <si>
+    <t>CP-MLI-069046217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 16:50:09</t>
+  </si>
+  <si>
+    <t>CP-MLI-069047217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 16:52:37</t>
+  </si>
+  <si>
+    <t>CP-MLI-069048217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 16:55:00</t>
+  </si>
+  <si>
+    <t>CP-MLI-069049217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 16:57:30</t>
+  </si>
+  <si>
+    <t>CP-MLI-069051217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 16:59:54</t>
+  </si>
+  <si>
+    <t>CP-MLI-069052217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 17:02:32</t>
+  </si>
+  <si>
+    <t>CP-MLI-069053217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 17:05:14</t>
+  </si>
+  <si>
+    <t>CP-MLI-069054217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 17:07:53</t>
+  </si>
+  <si>
+    <t>CP-MLI-069055217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 17:10:28</t>
+  </si>
+  <si>
+    <t>CP-MLI-069057217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 17:35:46</t>
+  </si>
+  <si>
+    <t>CP-MLI-069065217</t>
+  </si>
+  <si>
+    <t>05/08/2026, 18:08:53</t>
+  </si>
+  <si>
+    <t>DA-MLI-069247218</t>
+  </si>
+  <si>
+    <t>TC_REG_034 | Create Claim on a live policy, update Claim Information and complete claim</t>
+  </si>
+  <si>
+    <t>06/08/2026, 12:25:35</t>
+  </si>
+  <si>
+    <t>DA-MLI-069252218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 12:36:55</t>
+  </si>
+  <si>
+    <t>DA-MLI-069253218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 12:42:03</t>
+  </si>
+  <si>
+    <t>DA-MLI-069254218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 12:51:02</t>
+  </si>
+  <si>
+    <t>DA-MLI-069260218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 12:55:50</t>
+  </si>
+  <si>
+    <t>DA-MLI-069261218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 13:01:55</t>
+  </si>
+  <si>
+    <t>DA-MLI-069262218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 13:09:09</t>
+  </si>
+  <si>
+    <t>DA-MLI-069263218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 13:15:00</t>
+  </si>
+  <si>
+    <t>DA-MLI-069264218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 13:19:10</t>
+  </si>
+  <si>
+    <t>DA-MLI-069265218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 13:28:45</t>
+  </si>
+  <si>
+    <t>DA-MLI-069266218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 13:36:15</t>
+  </si>
+  <si>
+    <t>DA-MLI-069267218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 13:39:50</t>
+  </si>
+  <si>
+    <t>DA-MLI-069268218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 13:44:29</t>
+  </si>
+  <si>
+    <t>DA-MLI-069270218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 13:53:37</t>
+  </si>
+  <si>
+    <t>DA-MLI-069271218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 13:58:33</t>
+  </si>
+  <si>
+    <t>DA-MLI-069272218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 14:02:57</t>
+  </si>
+  <si>
+    <t>DA-MLI-069277218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 14:07:42</t>
+  </si>
+  <si>
+    <t>DA-MLI-069280218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 14:18:03</t>
+  </si>
+  <si>
+    <t>DA-MLI-069281218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 14:28:07</t>
+  </si>
+  <si>
+    <t>DA-MLI-069289218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 14:51:24</t>
+  </si>
+  <si>
+    <t>DA-MLI-069290218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 14:54:56</t>
+  </si>
+  <si>
+    <t>DA-MLI-069292218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 15:01:57</t>
+  </si>
+  <si>
+    <t>DA-MLI-069293218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 15:04:59</t>
+  </si>
+  <si>
+    <t>DA-MLI-069294218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 15:10:44</t>
+  </si>
+  <si>
+    <t>DA-MLI-069295218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 15:14:16</t>
+  </si>
+  <si>
+    <t>DA-MLI-069326218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 15:17:38</t>
+  </si>
+  <si>
+    <t>DA-MLI-069327218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 15:21:37</t>
+  </si>
+  <si>
+    <t>DA-MLI-069328218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 15:25:48</t>
+  </si>
+  <si>
+    <t>DA-MLI-069329218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 15:30:25</t>
+  </si>
+  <si>
+    <t>DA-MLI-069330218</t>
+  </si>
+  <si>
+    <t>06/08/2026, 15:41:06</t>
   </si>
 </sst>
 </file>
@@ -4515,7 +5001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F634"/>
+  <dimension ref="A1:F714"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -17206,6 +17692,1606 @@
         <v>1356</v>
       </c>
     </row>
+    <row r="635" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A635" s="4">
+        <v>634</v>
+      </c>
+      <c r="B635" s="5" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C635" s="5" t="s">
+        <v>933</v>
+      </c>
+      <c r="D635" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E635" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F635" s="5" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="636" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A636" s="2">
+        <v>635</v>
+      </c>
+      <c r="B636" s="3" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C636" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D636" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E636" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F636" s="3" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="637" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A637" s="4">
+        <v>636</v>
+      </c>
+      <c r="B637" s="5" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C637" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D637" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E637" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F637" s="5" t="s">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="638" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A638" s="2">
+        <v>637</v>
+      </c>
+      <c r="B638" s="3" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C638" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D638" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E638" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F638" s="3" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="639" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A639" s="4">
+        <v>638</v>
+      </c>
+      <c r="B639" s="5" t="s">
+        <v>1365</v>
+      </c>
+      <c r="C639" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D639" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E639" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F639" s="5" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="640" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A640" s="2">
+        <v>639</v>
+      </c>
+      <c r="B640" s="3" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C640" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D640" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E640" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F640" s="3" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="641" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A641" s="4">
+        <v>640</v>
+      </c>
+      <c r="B641" s="5" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C641" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D641" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E641" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F641" s="5" t="s">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="642" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A642" s="2">
+        <v>641</v>
+      </c>
+      <c r="B642" s="3" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C642" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D642" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E642" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F642" s="3" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="643" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A643" s="4">
+        <v>642</v>
+      </c>
+      <c r="B643" s="5" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C643" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D643" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E643" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F643" s="5" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="644" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A644" s="2">
+        <v>643</v>
+      </c>
+      <c r="B644" s="3" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C644" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D644" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E644" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F644" s="3" t="s">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="645" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A645" s="4">
+        <v>644</v>
+      </c>
+      <c r="B645" s="5" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C645" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D645" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E645" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F645" s="5" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="646" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A646" s="2">
+        <v>645</v>
+      </c>
+      <c r="B646" s="3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C646" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D646" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E646" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F646" s="3" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="647" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A647" s="4">
+        <v>646</v>
+      </c>
+      <c r="B647" s="5" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C647" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D647" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E647" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F647" s="5" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="648" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A648" s="2">
+        <v>647</v>
+      </c>
+      <c r="B648" s="3" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C648" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D648" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E648" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F648" s="3" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="649" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A649" s="4">
+        <v>648</v>
+      </c>
+      <c r="B649" s="5" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C649" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D649" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E649" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F649" s="5" t="s">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="650" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A650" s="2">
+        <v>649</v>
+      </c>
+      <c r="B650" s="3" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C650" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D650" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E650" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F650" s="3" t="s">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="651" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A651" s="4">
+        <v>650</v>
+      </c>
+      <c r="B651" s="5" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C651" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D651" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E651" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F651" s="5" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="652" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A652" s="2">
+        <v>651</v>
+      </c>
+      <c r="B652" s="3" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C652" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D652" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E652" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F652" s="3" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="653" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A653" s="4">
+        <v>652</v>
+      </c>
+      <c r="B653" s="5" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C653" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D653" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E653" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F653" s="5" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="654" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A654" s="2">
+        <v>653</v>
+      </c>
+      <c r="B654" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C654" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D654" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E654" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F654" s="3" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="655" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A655" s="4">
+        <v>654</v>
+      </c>
+      <c r="B655" s="5" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C655" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D655" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E655" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F655" s="5" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="656" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A656" s="2">
+        <v>655</v>
+      </c>
+      <c r="B656" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C656" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D656" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E656" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F656" s="3" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="657" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A657" s="4">
+        <v>656</v>
+      </c>
+      <c r="B657" s="5" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C657" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D657" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E657" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F657" s="5" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="658" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A658" s="2">
+        <v>657</v>
+      </c>
+      <c r="B658" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C658" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D658" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E658" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F658" s="3" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="659" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A659" s="4">
+        <v>658</v>
+      </c>
+      <c r="B659" s="5" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C659" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D659" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E659" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F659" s="5" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="660" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A660" s="2">
+        <v>659</v>
+      </c>
+      <c r="B660" s="3" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C660" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D660" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E660" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F660" s="3" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="661" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A661" s="4">
+        <v>660</v>
+      </c>
+      <c r="B661" s="5" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C661" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D661" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E661" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F661" s="5" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="662" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A662" s="2">
+        <v>661</v>
+      </c>
+      <c r="B662" s="3" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C662" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D662" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E662" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F662" s="3" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="663" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A663" s="4">
+        <v>662</v>
+      </c>
+      <c r="B663" s="5" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C663" s="5" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D663" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E663" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F663" s="5" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="664" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A664" s="2">
+        <v>663</v>
+      </c>
+      <c r="B664" s="3" t="s">
+        <v>1416</v>
+      </c>
+      <c r="C664" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D664" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E664" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F664" s="3" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="665" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A665" s="4">
+        <v>664</v>
+      </c>
+      <c r="B665" s="5" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C665" s="5" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D665" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E665" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F665" s="5" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="666" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A666" s="2">
+        <v>665</v>
+      </c>
+      <c r="B666" s="3" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C666" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D666" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E666" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F666" s="3" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="667" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A667" s="4">
+        <v>666</v>
+      </c>
+      <c r="B667" s="5" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C667" s="5" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D667" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E667" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F667" s="5" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="668" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A668" s="2">
+        <v>667</v>
+      </c>
+      <c r="B668" s="3" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C668" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D668" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E668" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F668" s="3" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="669" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A669" s="4">
+        <v>668</v>
+      </c>
+      <c r="B669" s="5" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C669" s="5" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D669" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E669" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F669" s="5" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="670" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A670" s="2">
+        <v>669</v>
+      </c>
+      <c r="B670" s="3" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C670" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D670" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E670" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F670" s="3" t="s">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="671" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A671" s="4">
+        <v>670</v>
+      </c>
+      <c r="B671" s="5" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C671" s="5" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D671" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E671" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F671" s="5" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="672" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A672" s="2">
+        <v>671</v>
+      </c>
+      <c r="B672" s="3" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C672" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D672" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E672" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F672" s="3" t="s">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="673" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A673" s="4">
+        <v>672</v>
+      </c>
+      <c r="B673" s="5" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C673" s="5" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D673" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E673" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F673" s="5" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="674" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A674" s="2">
+        <v>673</v>
+      </c>
+      <c r="B674" s="3" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C674" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D674" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E674" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F674" s="3" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="675" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A675" s="4">
+        <v>674</v>
+      </c>
+      <c r="B675" s="5" t="s">
+        <v>1438</v>
+      </c>
+      <c r="C675" s="5" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D675" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E675" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F675" s="5" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="676" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A676" s="2">
+        <v>675</v>
+      </c>
+      <c r="B676" s="3" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C676" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D676" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E676" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F676" s="3" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="677" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A677" s="4">
+        <v>676</v>
+      </c>
+      <c r="B677" s="5" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C677" s="5" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D677" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E677" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F677" s="5" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="678" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A678" s="2">
+        <v>677</v>
+      </c>
+      <c r="B678" s="3" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C678" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D678" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E678" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F678" s="3" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="679" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A679" s="4">
+        <v>678</v>
+      </c>
+      <c r="B679" s="5" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C679" s="5" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D679" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E679" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F679" s="5" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="680" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A680" s="2">
+        <v>679</v>
+      </c>
+      <c r="B680" s="3" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C680" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D680" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E680" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F680" s="3" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="681" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A681" s="4">
+        <v>680</v>
+      </c>
+      <c r="B681" s="5" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C681" s="5" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D681" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E681" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F681" s="5" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="682" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A682" s="2">
+        <v>681</v>
+      </c>
+      <c r="B682" s="3" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C682" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D682" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E682" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F682" s="3" t="s">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="683" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A683" s="4">
+        <v>682</v>
+      </c>
+      <c r="B683" s="5" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C683" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D683" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E683" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F683" s="5" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="684" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A684" s="2">
+        <v>683</v>
+      </c>
+      <c r="B684" s="3" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C684" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D684" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E684" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F684" s="3" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="685" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A685" s="4">
+        <v>684</v>
+      </c>
+      <c r="B685" s="5" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C685" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D685" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E685" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F685" s="5" t="s">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="686" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A686" s="2">
+        <v>685</v>
+      </c>
+      <c r="B686" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C686" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D686" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E686" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F686" s="3" t="s">
+        <v>1462</v>
+      </c>
+    </row>
+    <row r="687" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A687" s="4">
+        <v>686</v>
+      </c>
+      <c r="B687" s="5" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C687" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D687" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E687" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F687" s="5" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="688" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A688" s="2">
+        <v>687</v>
+      </c>
+      <c r="B688" s="3" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C688" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D688" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E688" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F688" s="3" t="s">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="689" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A689" s="4">
+        <v>688</v>
+      </c>
+      <c r="B689" s="5" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C689" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D689" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E689" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F689" s="5" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="690" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A690" s="2">
+        <v>689</v>
+      </c>
+      <c r="B690" s="3" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C690" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D690" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E690" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F690" s="3" t="s">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="691" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A691" s="4">
+        <v>690</v>
+      </c>
+      <c r="B691" s="5" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C691" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D691" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E691" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F691" s="5" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="692" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A692" s="2">
+        <v>691</v>
+      </c>
+      <c r="B692" s="3" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C692" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D692" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E692" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F692" s="3" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="693" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A693" s="4">
+        <v>692</v>
+      </c>
+      <c r="B693" s="5" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C693" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D693" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E693" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F693" s="5" t="s">
+        <v>1476</v>
+      </c>
+    </row>
+    <row r="694" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A694" s="2">
+        <v>693</v>
+      </c>
+      <c r="B694" s="3" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C694" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D694" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E694" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F694" s="3" t="s">
+        <v>1478</v>
+      </c>
+    </row>
+    <row r="695" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A695" s="4">
+        <v>694</v>
+      </c>
+      <c r="B695" s="5" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C695" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D695" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E695" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F695" s="5" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="696" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A696" s="2">
+        <v>695</v>
+      </c>
+      <c r="B696" s="3" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C696" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D696" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E696" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F696" s="3" t="s">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="697" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A697" s="4">
+        <v>696</v>
+      </c>
+      <c r="B697" s="5" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C697" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D697" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E697" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F697" s="5" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="698" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A698" s="2">
+        <v>697</v>
+      </c>
+      <c r="B698" s="3" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C698" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D698" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E698" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F698" s="3" t="s">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="699" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A699" s="4">
+        <v>698</v>
+      </c>
+      <c r="B699" s="5" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C699" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D699" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E699" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F699" s="5" t="s">
+        <v>1488</v>
+      </c>
+    </row>
+    <row r="700" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A700" s="2">
+        <v>699</v>
+      </c>
+      <c r="B700" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C700" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D700" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E700" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F700" s="3" t="s">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="701" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A701" s="4">
+        <v>700</v>
+      </c>
+      <c r="B701" s="5" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C701" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D701" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E701" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F701" s="5" t="s">
+        <v>1492</v>
+      </c>
+    </row>
+    <row r="702" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A702" s="2">
+        <v>701</v>
+      </c>
+      <c r="B702" s="3" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C702" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D702" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E702" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F702" s="3" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="703" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A703" s="4">
+        <v>702</v>
+      </c>
+      <c r="B703" s="5" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C703" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D703" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E703" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F703" s="5" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="704" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A704" s="2">
+        <v>703</v>
+      </c>
+      <c r="B704" s="3" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C704" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D704" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E704" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F704" s="3" t="s">
+        <v>1498</v>
+      </c>
+    </row>
+    <row r="705" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A705" s="4">
+        <v>704</v>
+      </c>
+      <c r="B705" s="5" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C705" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D705" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E705" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F705" s="5" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="706" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A706" s="2">
+        <v>705</v>
+      </c>
+      <c r="B706" s="3" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C706" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D706" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E706" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F706" s="3" t="s">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="707" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A707" s="4">
+        <v>706</v>
+      </c>
+      <c r="B707" s="5" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C707" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D707" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E707" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F707" s="5" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="708" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A708" s="2">
+        <v>707</v>
+      </c>
+      <c r="B708" s="3" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C708" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D708" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E708" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F708" s="3" t="s">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="709" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A709" s="4">
+        <v>708</v>
+      </c>
+      <c r="B709" s="5" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C709" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D709" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E709" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F709" s="5" t="s">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="710" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A710" s="2">
+        <v>709</v>
+      </c>
+      <c r="B710" s="3" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C710" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D710" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E710" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F710" s="3" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="711" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A711" s="4">
+        <v>710</v>
+      </c>
+      <c r="B711" s="5" t="s">
+        <v>1511</v>
+      </c>
+      <c r="C711" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D711" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E711" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F711" s="5" t="s">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="712" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A712" s="2">
+        <v>711</v>
+      </c>
+      <c r="B712" s="3" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C712" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D712" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E712" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F712" s="3" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="713" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A713" s="4">
+        <v>712</v>
+      </c>
+      <c r="B713" s="5" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C713" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D713" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E713" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F713" s="5" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="714" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A714" s="2">
+        <v>713</v>
+      </c>
+      <c r="B714" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C714" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D714" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E714" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F714" s="3" t="s">
+        <v>1518</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/reports/policy-tracker.xlsx
+++ b/reports/policy-tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3571" uniqueCount="1519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3671" uniqueCount="1559">
   <si>
     <t>Run #</t>
   </si>
@@ -4568,6 +4568,126 @@
   </si>
   <si>
     <t>06/08/2026, 15:41:06</t>
+  </si>
+  <si>
+    <t>CP-NI-069948222</t>
+  </si>
+  <si>
+    <t>10/08/2026, 17:10:10</t>
+  </si>
+  <si>
+    <t>CP-MLI-069953222</t>
+  </si>
+  <si>
+    <t>10/08/2026, 17:19:39</t>
+  </si>
+  <si>
+    <t>CP-MLI-069954222</t>
+  </si>
+  <si>
+    <t>10/08/2026, 17:20:21</t>
+  </si>
+  <si>
+    <t>CP-MLI-069955222</t>
+  </si>
+  <si>
+    <t>10/08/2026, 17:21:16</t>
+  </si>
+  <si>
+    <t>DA-MLI-069962222</t>
+  </si>
+  <si>
+    <t>10/08/2026, 17:26:35</t>
+  </si>
+  <si>
+    <t>DA-MLI-069969222</t>
+  </si>
+  <si>
+    <t>10/08/2026, 17:29:12</t>
+  </si>
+  <si>
+    <t>DA-MLI-069986222</t>
+  </si>
+  <si>
+    <t>10/08/2026, 17:30:45</t>
+  </si>
+  <si>
+    <t>DA-MLI-069993222</t>
+  </si>
+  <si>
+    <t>10/08/2026, 17:33:01</t>
+  </si>
+  <si>
+    <t>CP-MLI-070019222</t>
+  </si>
+  <si>
+    <t>10/08/2026, 17:37:22</t>
+  </si>
+  <si>
+    <t>DA-MLI-070157222</t>
+  </si>
+  <si>
+    <t>10/08/2026, 19:26:00</t>
+  </si>
+  <si>
+    <t>CP-MLI-070517222</t>
+  </si>
+  <si>
+    <t>10/08/2026, 20:10:45</t>
+  </si>
+  <si>
+    <t>CP-MLI-070556222</t>
+  </si>
+  <si>
+    <t>10/08/2026, 20:15:35</t>
+  </si>
+  <si>
+    <t>DA-MLI-070732222</t>
+  </si>
+  <si>
+    <t>10/08/2026, 20:37:31</t>
+  </si>
+  <si>
+    <t>CP-NI-070781222</t>
+  </si>
+  <si>
+    <t>10/08/2026, 20:44:35</t>
+  </si>
+  <si>
+    <t>DA-MLI-070843222</t>
+  </si>
+  <si>
+    <t>10/08/2026, 20:54:26</t>
+  </si>
+  <si>
+    <t>DA-MLI-070869222</t>
+  </si>
+  <si>
+    <t>10/08/2026, 20:58:51</t>
+  </si>
+  <si>
+    <t>CP-MLI-070917222</t>
+  </si>
+  <si>
+    <t>10/08/2026, 21:07:40</t>
+  </si>
+  <si>
+    <t>CP-MLI-070942222</t>
+  </si>
+  <si>
+    <t>10/08/2026, 21:11:35</t>
+  </si>
+  <si>
+    <t>DA-MLI-071535223</t>
+  </si>
+  <si>
+    <t>11/08/2026, 13:02:37</t>
+  </si>
+  <si>
+    <t>CP-MLI-071541223</t>
+  </si>
+  <si>
+    <t>11/08/2026, 13:35:20</t>
   </si>
 </sst>
 </file>
@@ -5001,7 +5121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F714"/>
+  <dimension ref="A1:F734"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -19292,6 +19412,406 @@
         <v>1518</v>
       </c>
     </row>
+    <row r="715" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A715" s="4">
+        <v>714</v>
+      </c>
+      <c r="B715" s="5" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C715" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D715" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="E715" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F715" s="5" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="716" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A716" s="2">
+        <v>715</v>
+      </c>
+      <c r="B716" s="3" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C716" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D716" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E716" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F716" s="3" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="717" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A717" s="4">
+        <v>716</v>
+      </c>
+      <c r="B717" s="5" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C717" s="5" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D717" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E717" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F717" s="5" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="718" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A718" s="2">
+        <v>717</v>
+      </c>
+      <c r="B718" s="3" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C718" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D718" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E718" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F718" s="3" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="719" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A719" s="4">
+        <v>718</v>
+      </c>
+      <c r="B719" s="5" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C719" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D719" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E719" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F719" s="5" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="720" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A720" s="2">
+        <v>719</v>
+      </c>
+      <c r="B720" s="3" t="s">
+        <v>1529</v>
+      </c>
+      <c r="C720" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D720" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E720" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F720" s="3" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="721" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A721" s="4">
+        <v>720</v>
+      </c>
+      <c r="B721" s="5" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C721" s="5" t="s">
+        <v>930</v>
+      </c>
+      <c r="D721" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E721" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F721" s="5" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="722" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A722" s="2">
+        <v>721</v>
+      </c>
+      <c r="B722" s="3" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C722" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="D722" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E722" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F722" s="3" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="723" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A723" s="4">
+        <v>722</v>
+      </c>
+      <c r="B723" s="5" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C723" s="5" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D723" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E723" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F723" s="5" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="724" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A724" s="2">
+        <v>723</v>
+      </c>
+      <c r="B724" s="3" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C724" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D724" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E724" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F724" s="3" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="725" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A725" s="4">
+        <v>724</v>
+      </c>
+      <c r="B725" s="5" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C725" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D725" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E725" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F725" s="5" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="726" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A726" s="2">
+        <v>725</v>
+      </c>
+      <c r="B726" s="3" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C726" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D726" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E726" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F726" s="3" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="727" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A727" s="4">
+        <v>726</v>
+      </c>
+      <c r="B727" s="5" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C727" s="5" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D727" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E727" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F727" s="5" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="728" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A728" s="2">
+        <v>727</v>
+      </c>
+      <c r="B728" s="3" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C728" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="D728" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E728" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F728" s="3" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="729" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A729" s="4">
+        <v>728</v>
+      </c>
+      <c r="B729" s="5" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C729" s="5" t="s">
+        <v>703</v>
+      </c>
+      <c r="D729" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E729" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F729" s="5" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="730" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A730" s="2">
+        <v>729</v>
+      </c>
+      <c r="B730" s="3" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C730" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="D730" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E730" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F730" s="3" t="s">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="731" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A731" s="4">
+        <v>730</v>
+      </c>
+      <c r="B731" s="5" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C731" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="D731" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E731" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F731" s="5" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="732" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A732" s="2">
+        <v>731</v>
+      </c>
+      <c r="B732" s="3" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C732" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D732" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E732" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F732" s="3" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="733" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A733" s="4">
+        <v>732</v>
+      </c>
+      <c r="B733" s="5" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C733" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="D733" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E733" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F733" s="5" t="s">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="734" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A734" s="2">
+        <v>733</v>
+      </c>
+      <c r="B734" s="3" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C734" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D734" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E734" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F734" s="3" t="s">
+        <v>1558</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/reports/policy-tracker.xlsx
+++ b/reports/policy-tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3671" uniqueCount="1559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3821" uniqueCount="1624">
   <si>
     <t>Run #</t>
   </si>
@@ -4688,6 +4688,201 @@
   </si>
   <si>
     <t>11/08/2026, 13:35:20</t>
+  </si>
+  <si>
+    <t>CP-MLI-543247223</t>
+  </si>
+  <si>
+    <t>11/08/2026, 14:33:40</t>
+  </si>
+  <si>
+    <t>CP-MLI-543250223</t>
+  </si>
+  <si>
+    <t>11/08/2026, 14:34:15</t>
+  </si>
+  <si>
+    <t>CP-MLI-543255223</t>
+  </si>
+  <si>
+    <t>11/08/2026, 14:34:58</t>
+  </si>
+  <si>
+    <t>DA-MLI-543268223</t>
+  </si>
+  <si>
+    <t>11/08/2026, 14:37:27</t>
+  </si>
+  <si>
+    <t>DA-MLI-543278223</t>
+  </si>
+  <si>
+    <t>11/08/2026, 14:39:22</t>
+  </si>
+  <si>
+    <t>DA-MLI-543288223</t>
+  </si>
+  <si>
+    <t>11/08/2026, 14:41:15</t>
+  </si>
+  <si>
+    <t>DA-MLI-543301223</t>
+  </si>
+  <si>
+    <t>11/08/2026, 14:43:24</t>
+  </si>
+  <si>
+    <t>DA-MLI-543318223</t>
+  </si>
+  <si>
+    <t>11/08/2026, 14:47:27</t>
+  </si>
+  <si>
+    <t>DA-MLI-071560223</t>
+  </si>
+  <si>
+    <t>11/08/2026, 14:51:06</t>
+  </si>
+  <si>
+    <t>CP-MLI-075083225</t>
+  </si>
+  <si>
+    <t>13/08/2026, 13:32:30</t>
+  </si>
+  <si>
+    <t>CP-MLI-075086225</t>
+  </si>
+  <si>
+    <t>13/08/2026, 13:43:55</t>
+  </si>
+  <si>
+    <t>0YTAd000002v385OAA</t>
+  </si>
+  <si>
+    <t>npx | Create Policy</t>
+  </si>
+  <si>
+    <t>Oliva Automation</t>
+  </si>
+  <si>
+    <t>SIT</t>
+  </si>
+  <si>
+    <t>13/08/2026, 15:43:10</t>
+  </si>
+  <si>
+    <t>0YTAd000002v39hOAA</t>
+  </si>
+  <si>
+    <t>13/08/2026, 16:01:08</t>
+  </si>
+  <si>
+    <t>0YTAd000002v3BJOAY</t>
+  </si>
+  <si>
+    <t>npx | Create Policy Version</t>
+  </si>
+  <si>
+    <t>13/08/2026, 16:04:15</t>
+  </si>
+  <si>
+    <t>0YTAd000002v3JNOAY</t>
+  </si>
+  <si>
+    <t>13/08/2026, 16:59:08</t>
+  </si>
+  <si>
+    <t>0YTAd000002v3MbOAI</t>
+  </si>
+  <si>
+    <t>13/08/2026, 17:02:26</t>
+  </si>
+  <si>
+    <t>0YTAd000002v3PpOAI</t>
+  </si>
+  <si>
+    <t>13/08/2026, 17:20:20</t>
+  </si>
+  <si>
+    <t>0YTAd000002v3RROAY</t>
+  </si>
+  <si>
+    <t>13/08/2026, 17:23:10</t>
+  </si>
+  <si>
+    <t>0YTAd000002v3T3OAI</t>
+  </si>
+  <si>
+    <t>13/08/2026, 17:42:05</t>
+  </si>
+  <si>
+    <t>0YTAd000002v3UfOAI</t>
+  </si>
+  <si>
+    <t>npx | Cancel and Reissue Policy</t>
+  </si>
+  <si>
+    <t>13/08/2026, 17:45:13</t>
+  </si>
+  <si>
+    <t>0YTAd000002v3WHOAY</t>
+  </si>
+  <si>
+    <t>13/08/2026, 17:48:46</t>
+  </si>
+  <si>
+    <t>0YTTA000002W7zh4AC</t>
+  </si>
+  <si>
+    <t>18/08/2026, 18:37:49</t>
+  </si>
+  <si>
+    <t>0YTTA000002WJrB4AW</t>
+  </si>
+  <si>
+    <t>19/08/2026, 09:34:22</t>
+  </si>
+  <si>
+    <t>0YTTA000002WJsn4AG</t>
+  </si>
+  <si>
+    <t>19/08/2026, 09:37:59</t>
+  </si>
+  <si>
+    <t>0YTTA000002WJuP4AW</t>
+  </si>
+  <si>
+    <t>19/08/2026, 09:41:16</t>
+  </si>
+  <si>
+    <t>0YTTA000002WLHt4AO</t>
+  </si>
+  <si>
+    <t>19/08/2026, 17:25:48</t>
+  </si>
+  <si>
+    <t>0YTTA000002WLJV4A4</t>
+  </si>
+  <si>
+    <t>19/08/2026, 17:29:33</t>
+  </si>
+  <si>
+    <t>0YTTA000002WLWP4A4</t>
+  </si>
+  <si>
+    <t>19/08/2026, 19:06:42</t>
+  </si>
+  <si>
+    <t>0YTTA000002WLY14AO</t>
+  </si>
+  <si>
+    <t>19/08/2026, 19:10:32</t>
+  </si>
+  <si>
+    <t>CP-MLI-076513233</t>
+  </si>
+  <si>
+    <t>21/08/2026, 14:11:42</t>
   </si>
 </sst>
 </file>
@@ -5121,7 +5316,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F734"/>
+  <dimension ref="A1:F764"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -19812,6 +20007,606 @@
         <v>1558</v>
       </c>
     </row>
+    <row r="735" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A735" s="4">
+        <v>734</v>
+      </c>
+      <c r="B735" s="5" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C735" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D735" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E735" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="F735" s="5" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="736" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A736" s="2">
+        <v>735</v>
+      </c>
+      <c r="B736" s="3" t="s">
+        <v>1561</v>
+      </c>
+      <c r="C736" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D736" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E736" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="F736" s="3" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="737" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A737" s="4">
+        <v>736</v>
+      </c>
+      <c r="B737" s="5" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C737" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D737" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E737" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="F737" s="5" t="s">
+        <v>1564</v>
+      </c>
+    </row>
+    <row r="738" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A738" s="2">
+        <v>737</v>
+      </c>
+      <c r="B738" s="3" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C738" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D738" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E738" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="F738" s="3" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="739" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A739" s="4">
+        <v>738</v>
+      </c>
+      <c r="B739" s="5" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C739" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D739" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E739" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="F739" s="5" t="s">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="740" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A740" s="2">
+        <v>739</v>
+      </c>
+      <c r="B740" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="C740" s="3" t="s">
+        <v>930</v>
+      </c>
+      <c r="D740" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E740" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="F740" s="3" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="741" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A741" s="4">
+        <v>740</v>
+      </c>
+      <c r="B741" s="5" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C741" s="5" t="s">
+        <v>933</v>
+      </c>
+      <c r="D741" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E741" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="F741" s="5" t="s">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="742" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A742" s="2">
+        <v>741</v>
+      </c>
+      <c r="B742" s="3" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C742" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D742" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E742" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="F742" s="3" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="743" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A743" s="4">
+        <v>742</v>
+      </c>
+      <c r="B743" s="5" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C743" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D743" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E743" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F743" s="5" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="744" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A744" s="2">
+        <v>743</v>
+      </c>
+      <c r="B744" s="3" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C744" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D744" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E744" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F744" s="3" t="s">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="745" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A745" s="4">
+        <v>744</v>
+      </c>
+      <c r="B745" s="5" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C745" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D745" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E745" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F745" s="5" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="746" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A746" s="2">
+        <v>745</v>
+      </c>
+      <c r="B746" s="3" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C746" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D746" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E746" s="3" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F746" s="3" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="747" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A747" s="4">
+        <v>746</v>
+      </c>
+      <c r="B747" s="5" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C747" s="5" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D747" s="5" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E747" s="5" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F747" s="5" t="s">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="748" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A748" s="2">
+        <v>747</v>
+      </c>
+      <c r="B748" s="3" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C748" s="3" t="s">
+        <v>1589</v>
+      </c>
+      <c r="D748" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E748" s="3" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F748" s="3" t="s">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="749" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A749" s="4">
+        <v>748</v>
+      </c>
+      <c r="B749" s="5" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C749" s="5" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D749" s="5" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E749" s="5" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F749" s="5" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="750" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A750" s="2">
+        <v>749</v>
+      </c>
+      <c r="B750" s="3" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C750" s="3" t="s">
+        <v>1589</v>
+      </c>
+      <c r="D750" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E750" s="3" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F750" s="3" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="751" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A751" s="4">
+        <v>750</v>
+      </c>
+      <c r="B751" s="5" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C751" s="5" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D751" s="5" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E751" s="5" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F751" s="5" t="s">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="752" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A752" s="2">
+        <v>751</v>
+      </c>
+      <c r="B752" s="3" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C752" s="3" t="s">
+        <v>1589</v>
+      </c>
+      <c r="D752" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E752" s="3" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F752" s="3" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="753" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A753" s="4">
+        <v>752</v>
+      </c>
+      <c r="B753" s="5" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C753" s="5" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D753" s="5" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E753" s="5" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F753" s="5" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="754" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A754" s="2">
+        <v>753</v>
+      </c>
+      <c r="B754" s="3" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C754" s="3" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D754" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E754" s="3" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F754" s="3" t="s">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="755" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A755" s="4">
+        <v>754</v>
+      </c>
+      <c r="B755" s="5" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C755" s="5" t="s">
+        <v>1589</v>
+      </c>
+      <c r="D755" s="5" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E755" s="5" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F755" s="5" t="s">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="756" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A756" s="2">
+        <v>755</v>
+      </c>
+      <c r="B756" s="3" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C756" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D756" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E756" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="F756" s="3" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="757" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A757" s="4">
+        <v>756</v>
+      </c>
+      <c r="B757" s="5" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C757" s="5" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D757" s="5" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E757" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="F757" s="5" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="758" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A758" s="2">
+        <v>757</v>
+      </c>
+      <c r="B758" s="3" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C758" s="3" t="s">
+        <v>1589</v>
+      </c>
+      <c r="D758" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E758" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="F758" s="3" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="759" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A759" s="4">
+        <v>758</v>
+      </c>
+      <c r="B759" s="5" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C759" s="5" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D759" s="5" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E759" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="F759" s="5" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="760" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A760" s="2">
+        <v>759</v>
+      </c>
+      <c r="B760" s="3" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C760" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D760" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E760" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="F760" s="3" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="761" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A761" s="4">
+        <v>760</v>
+      </c>
+      <c r="B761" s="5" t="s">
+        <v>1616</v>
+      </c>
+      <c r="C761" s="5" t="s">
+        <v>1589</v>
+      </c>
+      <c r="D761" s="5" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E761" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="F761" s="5" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="762" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A762" s="2">
+        <v>761</v>
+      </c>
+      <c r="B762" s="3" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C762" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D762" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E762" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="F762" s="3" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="763" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A763" s="4">
+        <v>762</v>
+      </c>
+      <c r="B763" s="5" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C763" s="5" t="s">
+        <v>1589</v>
+      </c>
+      <c r="D763" s="5" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E763" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="F763" s="5" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="764" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A764" s="2">
+        <v>763</v>
+      </c>
+      <c r="B764" s="3" t="s">
+        <v>1622</v>
+      </c>
+      <c r="C764" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D764" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E764" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="F764" s="3" t="s">
+        <v>1623</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/reports/policy-tracker.xlsx
+++ b/reports/policy-tracker.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3821" uniqueCount="1624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3856" uniqueCount="1638">
   <si>
     <t>Run #</t>
   </si>
@@ -4883,6 +4883,48 @@
   </si>
   <si>
     <t>21/08/2026, 14:11:42</t>
+  </si>
+  <si>
+    <t>CP-MLI-077227237</t>
+  </si>
+  <si>
+    <t>25/08/2026, 15:34:21</t>
+  </si>
+  <si>
+    <t>CP-MLI-545097237</t>
+  </si>
+  <si>
+    <t>25/08/2026, 17:09:13</t>
+  </si>
+  <si>
+    <t>CP-MLI-545098237</t>
+  </si>
+  <si>
+    <t>25/08/2026, 17:12:01</t>
+  </si>
+  <si>
+    <t>CP-MLI-545099237</t>
+  </si>
+  <si>
+    <t>25/08/2026, 17:14:32</t>
+  </si>
+  <si>
+    <t>CP-MLI-545101237</t>
+  </si>
+  <si>
+    <t>25/08/2026, 17:17:21</t>
+  </si>
+  <si>
+    <t>CP-MLI-545104237</t>
+  </si>
+  <si>
+    <t>25/08/2026, 17:24:05</t>
+  </si>
+  <si>
+    <t>CP-MLI-545107237</t>
+  </si>
+  <si>
+    <t>25/08/2026, 17:31:08</t>
   </si>
 </sst>
 </file>
@@ -5316,7 +5358,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F764"/>
+  <dimension ref="A1:F771"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -20607,6 +20649,146 @@
         <v>1623</v>
       </c>
     </row>
+    <row r="765" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A765" s="4">
+        <v>764</v>
+      </c>
+      <c r="B765" s="5" t="s">
+        <v>1624</v>
+      </c>
+      <c r="C765" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D765" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E765" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="F765" s="5" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="766" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A766" s="2">
+        <v>765</v>
+      </c>
+      <c r="B766" s="3" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C766" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D766" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E766" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="F766" s="3" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="767" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A767" s="4">
+        <v>766</v>
+      </c>
+      <c r="B767" s="5" t="s">
+        <v>1628</v>
+      </c>
+      <c r="C767" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D767" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E767" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="F767" s="5" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="768" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A768" s="2">
+        <v>767</v>
+      </c>
+      <c r="B768" s="3" t="s">
+        <v>1630</v>
+      </c>
+      <c r="C768" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D768" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E768" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="F768" s="3" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="769" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A769" s="4">
+        <v>768</v>
+      </c>
+      <c r="B769" s="5" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C769" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D769" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E769" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="F769" s="5" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="770" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A770" s="2">
+        <v>769</v>
+      </c>
+      <c r="B770" s="3" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C770" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D770" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E770" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="F770" s="3" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="771" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A771" s="4">
+        <v>770</v>
+      </c>
+      <c r="B771" s="5" t="s">
+        <v>1636</v>
+      </c>
+      <c r="C771" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D771" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E771" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="F771" s="5" t="s">
+        <v>1637</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/reports/policy-tracker.xlsx
+++ b/reports/policy-tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4091" uniqueCount="1732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4236" uniqueCount="1795">
   <si>
     <t>Run #</t>
   </si>
@@ -5210,6 +5210,195 @@
   </si>
   <si>
     <t>02/09/2026, 15:16:55</t>
+  </si>
+  <si>
+    <t>DA-MLI-549108245</t>
+  </si>
+  <si>
+    <t>02/09/2026, 20:12:40</t>
+  </si>
+  <si>
+    <t>DA-MLI-549109245</t>
+  </si>
+  <si>
+    <t>02/09/2026, 20:15:28</t>
+  </si>
+  <si>
+    <t>DA-MLI-549110245</t>
+  </si>
+  <si>
+    <t>02/09/2026, 20:19:59</t>
+  </si>
+  <si>
+    <t>DA-MLI-549111245</t>
+  </si>
+  <si>
+    <t>02/09/2026, 20:25:39</t>
+  </si>
+  <si>
+    <t>DA-MLI-549112245</t>
+  </si>
+  <si>
+    <t>02/09/2026, 20:35:34</t>
+  </si>
+  <si>
+    <t>DA-MLI-079766246</t>
+  </si>
+  <si>
+    <t>TC_REG_058 | NB-CNR | Validate CR0299 field in BDX line</t>
+  </si>
+  <si>
+    <t>03/09/2026, 15:49:27</t>
+  </si>
+  <si>
+    <t>DA-MLI-079769246</t>
+  </si>
+  <si>
+    <t>TC_REG_059 | NB-CNR | Validate CR0299 field for paid and written BDX lines</t>
+  </si>
+  <si>
+    <t>03/09/2026, 16:07:55</t>
+  </si>
+  <si>
+    <t>DA-MLI-079771246</t>
+  </si>
+  <si>
+    <t>03/09/2026, 16:14:33</t>
+  </si>
+  <si>
+    <t>DA-MLI-079774246</t>
+  </si>
+  <si>
+    <t>03/09/2026, 16:18:03</t>
+  </si>
+  <si>
+    <t>DA-MLI-079776246</t>
+  </si>
+  <si>
+    <t>03/09/2026, 16:24:30</t>
+  </si>
+  <si>
+    <t>DA-MLI-079778246</t>
+  </si>
+  <si>
+    <t>03/09/2026, 16:30:54</t>
+  </si>
+  <si>
+    <t>DA-MLI-079780246</t>
+  </si>
+  <si>
+    <t>03/09/2026, 16:37:24</t>
+  </si>
+  <si>
+    <t>DA-MLI-079782246</t>
+  </si>
+  <si>
+    <t>03/09/2026, 16:44:26</t>
+  </si>
+  <si>
+    <t>DA-MLI-079784246</t>
+  </si>
+  <si>
+    <t>03/09/2026, 16:49:35</t>
+  </si>
+  <si>
+    <t>DA-MLI-079786246</t>
+  </si>
+  <si>
+    <t>03/09/2026, 16:55:59</t>
+  </si>
+  <si>
+    <t>DA-MLI-079788246</t>
+  </si>
+  <si>
+    <t>03/09/2026, 17:02:56</t>
+  </si>
+  <si>
+    <t>DA-MLI-549316246</t>
+  </si>
+  <si>
+    <t>03/09/2026, 17:07:04</t>
+  </si>
+  <si>
+    <t>DA-MLI-549323246</t>
+  </si>
+  <si>
+    <t>03/09/2026, 17:08:58</t>
+  </si>
+  <si>
+    <t>DA-MLI-549332246</t>
+  </si>
+  <si>
+    <t>03/09/2026, 17:11:06</t>
+  </si>
+  <si>
+    <t>CP-NI-549362246</t>
+  </si>
+  <si>
+    <t>03/09/2026, 17:15:52</t>
+  </si>
+  <si>
+    <t>DA-MLI-549366246</t>
+  </si>
+  <si>
+    <t>03/09/2026, 17:16:12</t>
+  </si>
+  <si>
+    <t>DA-MLI-549477246</t>
+  </si>
+  <si>
+    <t>03/09/2026, 17:30:49</t>
+  </si>
+  <si>
+    <t>DA-MLI-079793246</t>
+  </si>
+  <si>
+    <t>TC_REG_058 | NB-CNR-Can | Validate CR0299 field in BDX line</t>
+  </si>
+  <si>
+    <t>03/09/2026, 18:20:33</t>
+  </si>
+  <si>
+    <t>DA-MLI-080227250</t>
+  </si>
+  <si>
+    <t>TC_REG_059 | NB-CNR-Can | Validate CR0299 field for paid and written BDX lines</t>
+  </si>
+  <si>
+    <t>07/09/2026, 10:12:11</t>
+  </si>
+  <si>
+    <t>DA-MLI-080229250</t>
+  </si>
+  <si>
+    <t>DT-MLIS-DF29.0.0 | F-232588 | CR-232467 | Validate CR0055 Deductible or Excess Basis after NB-CNR-MTA-MTA-Cancellation</t>
+  </si>
+  <si>
+    <t>07/09/2026, 10:22:34</t>
+  </si>
+  <si>
+    <t>DA-MLI-080233250</t>
+  </si>
+  <si>
+    <t>07/09/2026, 10:31:45</t>
+  </si>
+  <si>
+    <t>DA-MLI-080236250</t>
+  </si>
+  <si>
+    <t>07/09/2026, 10:39:55</t>
+  </si>
+  <si>
+    <t>DA-MLI-080239250</t>
+  </si>
+  <si>
+    <t>07/09/2026, 10:47:39</t>
+  </si>
+  <si>
+    <t>DA-MLI-080242250</t>
+  </si>
+  <si>
+    <t>07/09/2026, 10:53:27</t>
   </si>
 </sst>
 </file>
@@ -5244,7 +5433,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5269,6 +5458,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -5329,7 +5523,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5365,6 +5559,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5672,7 +5872,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F818"/>
+  <dimension ref="A1:F847"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -22043,6 +22243,586 @@
         <v>1731</v>
       </c>
     </row>
+    <row r="819" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A819" s="13">
+        <v>818</v>
+      </c>
+      <c r="B819" s="14" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C819" s="14" t="s">
+        <v>472</v>
+      </c>
+      <c r="D819" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E819" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F819" s="14" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="820" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A820" s="11">
+        <v>819</v>
+      </c>
+      <c r="B820" s="12" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C820" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="D820" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E820" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F820" s="12" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="821" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A821" s="13">
+        <v>820</v>
+      </c>
+      <c r="B821" s="14" t="s">
+        <v>1736</v>
+      </c>
+      <c r="C821" s="14" t="s">
+        <v>472</v>
+      </c>
+      <c r="D821" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E821" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F821" s="14" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="822" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A822" s="11">
+        <v>821</v>
+      </c>
+      <c r="B822" s="12" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C822" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="D822" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E822" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F822" s="12" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="823" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A823" s="13">
+        <v>822</v>
+      </c>
+      <c r="B823" s="14" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C823" s="14" t="s">
+        <v>472</v>
+      </c>
+      <c r="D823" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E823" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F823" s="14" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="824" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A824" s="11">
+        <v>823</v>
+      </c>
+      <c r="B824" s="12" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C824" s="12" t="s">
+        <v>1743</v>
+      </c>
+      <c r="D824" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E824" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F824" s="12" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="825" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A825" s="13">
+        <v>824</v>
+      </c>
+      <c r="B825" s="14" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C825" s="14" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D825" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E825" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F825" s="14" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="826" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A826" s="11">
+        <v>825</v>
+      </c>
+      <c r="B826" s="12" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C826" s="12" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D826" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E826" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F826" s="12" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="827" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A827" s="13">
+        <v>826</v>
+      </c>
+      <c r="B827" s="14" t="s">
+        <v>1750</v>
+      </c>
+      <c r="C827" s="14" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D827" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E827" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F827" s="14" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="828" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A828" s="11">
+        <v>827</v>
+      </c>
+      <c r="B828" s="12" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C828" s="12" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D828" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E828" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F828" s="12" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="829" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A829" s="13">
+        <v>828</v>
+      </c>
+      <c r="B829" s="14" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C829" s="14" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D829" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E829" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F829" s="14" t="s">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="830" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A830" s="11">
+        <v>829</v>
+      </c>
+      <c r="B830" s="12" t="s">
+        <v>1756</v>
+      </c>
+      <c r="C830" s="12" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D830" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E830" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F830" s="12" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="831" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A831" s="13">
+        <v>830</v>
+      </c>
+      <c r="B831" s="14" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C831" s="14" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D831" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E831" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F831" s="14" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="832" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A832" s="11">
+        <v>831</v>
+      </c>
+      <c r="B832" s="12" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C832" s="12" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D832" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E832" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F832" s="12" t="s">
+        <v>1761</v>
+      </c>
+    </row>
+    <row r="833" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A833" s="13">
+        <v>832</v>
+      </c>
+      <c r="B833" s="14" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C833" s="14" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D833" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E833" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F833" s="14" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="834" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A834" s="11">
+        <v>833</v>
+      </c>
+      <c r="B834" s="12" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C834" s="12" t="s">
+        <v>1746</v>
+      </c>
+      <c r="D834" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E834" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F834" s="12" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="835" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A835" s="13">
+        <v>834</v>
+      </c>
+      <c r="B835" s="14" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C835" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D835" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E835" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F835" s="14" t="s">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="836" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A836" s="11">
+        <v>835</v>
+      </c>
+      <c r="B836" s="12" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C836" s="12" t="s">
+        <v>930</v>
+      </c>
+      <c r="D836" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E836" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F836" s="12" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="837" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A837" s="13">
+        <v>836</v>
+      </c>
+      <c r="B837" s="14" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C837" s="14" t="s">
+        <v>933</v>
+      </c>
+      <c r="D837" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E837" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F837" s="14" t="s">
+        <v>1771</v>
+      </c>
+    </row>
+    <row r="838" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A838" s="11">
+        <v>837</v>
+      </c>
+      <c r="B838" s="12" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C838" s="12" t="s">
+        <v>943</v>
+      </c>
+      <c r="D838" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="E838" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F838" s="12" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="839" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A839" s="13">
+        <v>838</v>
+      </c>
+      <c r="B839" s="14" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C839" s="14" t="s">
+        <v>780</v>
+      </c>
+      <c r="D839" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E839" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F839" s="14" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="840" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A840" s="11">
+        <v>839</v>
+      </c>
+      <c r="B840" s="12" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C840" s="12" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D840" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E840" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F840" s="12" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="841" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A841" s="13">
+        <v>840</v>
+      </c>
+      <c r="B841" s="14" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C841" s="14" t="s">
+        <v>1779</v>
+      </c>
+      <c r="D841" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E841" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F841" s="14" t="s">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="842" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A842" s="11">
+        <v>841</v>
+      </c>
+      <c r="B842" s="12" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C842" s="12" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D842" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E842" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F842" s="12" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="843" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A843" s="13">
+        <v>842</v>
+      </c>
+      <c r="B843" s="14" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C843" s="14" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D843" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E843" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F843" s="14" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="844" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A844" s="11">
+        <v>843</v>
+      </c>
+      <c r="B844" s="12" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C844" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D844" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E844" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F844" s="12" t="s">
+        <v>1788</v>
+      </c>
+    </row>
+    <row r="845" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A845" s="13">
+        <v>844</v>
+      </c>
+      <c r="B845" s="14" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C845" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="D845" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E845" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F845" s="14" t="s">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="846" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A846" s="11">
+        <v>845</v>
+      </c>
+      <c r="B846" s="12" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C846" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D846" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E846" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F846" s="12" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="847" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A847" s="13">
+        <v>846</v>
+      </c>
+      <c r="B847" s="14" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C847" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="D847" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E847" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F847" s="14" t="s">
+        <v>1794</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/policy-tracker.xlsx
+++ b/reports/policy-tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4236" uniqueCount="1795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4276" uniqueCount="1812">
   <si>
     <t>Run #</t>
   </si>
@@ -5399,6 +5399,57 @@
   </si>
   <si>
     <t>07/09/2026, 10:53:27</t>
+  </si>
+  <si>
+    <t>CP-MLI-080346251</t>
+  </si>
+  <si>
+    <t>08/09/2026, 14:15:07</t>
+  </si>
+  <si>
+    <t>CP-MLI-550769251</t>
+  </si>
+  <si>
+    <t>08/09/2026, 14:22:05</t>
+  </si>
+  <si>
+    <t>CP-MLI-550770251</t>
+  </si>
+  <si>
+    <t>08/09/2026, 14:28:48</t>
+  </si>
+  <si>
+    <t>CP-MLI-550771251</t>
+  </si>
+  <si>
+    <t>08/09/2026, 14:35:49</t>
+  </si>
+  <si>
+    <t>CP-MLI-550773251</t>
+  </si>
+  <si>
+    <t>08/09/2026, 14:43:45</t>
+  </si>
+  <si>
+    <t>CP-MLI-550774251</t>
+  </si>
+  <si>
+    <t>08/09/2026, 14:48:44</t>
+  </si>
+  <si>
+    <t>CP-MLI-550776251</t>
+  </si>
+  <si>
+    <t>08/09/2026, 14:59:46</t>
+  </si>
+  <si>
+    <t>CP-MLI-550777251</t>
+  </si>
+  <si>
+    <t>TC_REG_034_COMM_FIN | Create claim and update Claim Loss Amounts (Estimates) then save</t>
+  </si>
+  <si>
+    <t>08/09/2026, 15:05:29</t>
   </si>
 </sst>
 </file>
@@ -5872,7 +5923,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F847"/>
+  <dimension ref="A1:F855"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -22823,6 +22874,166 @@
         <v>1794</v>
       </c>
     </row>
+    <row r="848" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A848" s="11">
+        <v>847</v>
+      </c>
+      <c r="B848" s="12" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C848" s="12" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D848" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E848" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F848" s="12" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="849" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A849" s="13">
+        <v>848</v>
+      </c>
+      <c r="B849" s="14" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C849" s="14" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D849" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E849" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F849" s="14" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="850" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A850" s="11">
+        <v>849</v>
+      </c>
+      <c r="B850" s="12" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C850" s="12" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D850" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E850" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F850" s="12" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="851" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A851" s="13">
+        <v>850</v>
+      </c>
+      <c r="B851" s="14" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C851" s="14" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D851" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E851" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F851" s="14" t="s">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="852" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A852" s="11">
+        <v>851</v>
+      </c>
+      <c r="B852" s="12" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C852" s="12" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D852" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E852" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F852" s="12" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="853" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A853" s="13">
+        <v>852</v>
+      </c>
+      <c r="B853" s="14" t="s">
+        <v>1805</v>
+      </c>
+      <c r="C853" s="14" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D853" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E853" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F853" s="14" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="854" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A854" s="11">
+        <v>853</v>
+      </c>
+      <c r="B854" s="12" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C854" s="12" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D854" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E854" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F854" s="12" t="s">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="855" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A855" s="13">
+        <v>854</v>
+      </c>
+      <c r="B855" s="14" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C855" s="14" t="s">
+        <v>1810</v>
+      </c>
+      <c r="D855" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E855" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F855" s="14" t="s">
+        <v>1811</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/policy-tracker.xlsx
+++ b/reports/policy-tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4276" uniqueCount="1812">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4376" uniqueCount="1853">
   <si>
     <t>Run #</t>
   </si>
@@ -5450,6 +5450,129 @@
   </si>
   <si>
     <t>08/09/2026, 15:05:29</t>
+  </si>
+  <si>
+    <t>CP-MLI-551182252</t>
+  </si>
+  <si>
+    <t>09/09/2026, 20:10:16</t>
+  </si>
+  <si>
+    <t>CP-MLI-551183252</t>
+  </si>
+  <si>
+    <t>09/09/2026, 20:11:00</t>
+  </si>
+  <si>
+    <t>CP-MLI-551184252</t>
+  </si>
+  <si>
+    <t>09/09/2026, 20:11:44</t>
+  </si>
+  <si>
+    <t>DA-MLI-551185252</t>
+  </si>
+  <si>
+    <t>09/09/2026, 20:12:37</t>
+  </si>
+  <si>
+    <t>DA-MLI-551186252</t>
+  </si>
+  <si>
+    <t>09/09/2026, 20:15:24</t>
+  </si>
+  <si>
+    <t>DA-MLI-551191252</t>
+  </si>
+  <si>
+    <t>09/09/2026, 20:35:21</t>
+  </si>
+  <si>
+    <t>DA-MLI-551193252</t>
+  </si>
+  <si>
+    <t>09/09/2026, 20:37:34</t>
+  </si>
+  <si>
+    <t>DA-MLI-551194252</t>
+  </si>
+  <si>
+    <t>09/09/2026, 20:40:14</t>
+  </si>
+  <si>
+    <t>DA-MLI-551196252</t>
+  </si>
+  <si>
+    <t>09/09/2026, 20:44:13</t>
+  </si>
+  <si>
+    <t>CP-MLI-551197252</t>
+  </si>
+  <si>
+    <t>09/09/2026, 20:46:43</t>
+  </si>
+  <si>
+    <t>CP-SC-551198252</t>
+  </si>
+  <si>
+    <t>09/09/2026, 20:48:03</t>
+  </si>
+  <si>
+    <t>CP-NI-551199252</t>
+  </si>
+  <si>
+    <t>09/09/2026, 20:52:06</t>
+  </si>
+  <si>
+    <t>DA-MLI-551203252</t>
+  </si>
+  <si>
+    <t>09/09/2026, 20:57:22</t>
+  </si>
+  <si>
+    <t>DA-MLI-551205252</t>
+  </si>
+  <si>
+    <t>09/09/2026, 20:59:58</t>
+  </si>
+  <si>
+    <t>DA-MLI-551207252</t>
+  </si>
+  <si>
+    <t>09/09/2026, 21:02:28</t>
+  </si>
+  <si>
+    <t>CP-NI-551211252</t>
+  </si>
+  <si>
+    <t>09/09/2026, 21:07:52</t>
+  </si>
+  <si>
+    <t>CP-NI-551214252</t>
+  </si>
+  <si>
+    <t>09/09/2026, 21:11:45</t>
+  </si>
+  <si>
+    <t>DA-MLI-080973257</t>
+  </si>
+  <si>
+    <t>TC_REG_CLAIMS_OPEN_CLAIM_COMPLETE | Create claim, fill Claim Information, and complete Open Claim</t>
+  </si>
+  <si>
+    <t>14/09/2026, 14:38:00</t>
+  </si>
+  <si>
+    <t>DA-MLI-080974257</t>
+  </si>
+  <si>
+    <t>14/09/2026, 14:46:18</t>
+  </si>
+  <si>
+    <t>DA-MLI-551800258</t>
+  </si>
+  <si>
+    <t>15/09/2026, 13:44:34</t>
   </si>
 </sst>
 </file>
@@ -5923,7 +6046,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F855"/>
+  <dimension ref="A1:F875"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -23034,6 +23157,406 @@
         <v>1811</v>
       </c>
     </row>
+    <row r="856" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A856" s="11">
+        <v>855</v>
+      </c>
+      <c r="B856" s="12" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C856" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D856" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E856" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F856" s="12" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="857" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A857" s="13">
+        <v>856</v>
+      </c>
+      <c r="B857" s="14" t="s">
+        <v>1814</v>
+      </c>
+      <c r="C857" s="14" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D857" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E857" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F857" s="14" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="858" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A858" s="11">
+        <v>857</v>
+      </c>
+      <c r="B858" s="12" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C858" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D858" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E858" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F858" s="12" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="859" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A859" s="13">
+        <v>858</v>
+      </c>
+      <c r="B859" s="14" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C859" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D859" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E859" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F859" s="14" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="860" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A860" s="11">
+        <v>859</v>
+      </c>
+      <c r="B860" s="12" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C860" s="12" t="s">
+        <v>930</v>
+      </c>
+      <c r="D860" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E860" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F860" s="12" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="861" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A861" s="13">
+        <v>860</v>
+      </c>
+      <c r="B861" s="14" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C861" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="D861" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E861" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F861" s="14" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="862" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A862" s="11">
+        <v>861</v>
+      </c>
+      <c r="B862" s="12" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C862" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D862" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E862" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F862" s="12" t="s">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="863" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A863" s="13">
+        <v>862</v>
+      </c>
+      <c r="B863" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="C863" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="D863" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E863" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F863" s="14" t="s">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="864" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A864" s="11">
+        <v>863</v>
+      </c>
+      <c r="B864" s="12" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C864" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D864" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E864" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F864" s="12" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="865" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A865" s="13">
+        <v>864</v>
+      </c>
+      <c r="B865" s="14" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C865" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="D865" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E865" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F865" s="14" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="866" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A866" s="11">
+        <v>865</v>
+      </c>
+      <c r="B866" s="12" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C866" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="D866" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E866" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F866" s="12" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="867" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A867" s="13">
+        <v>866</v>
+      </c>
+      <c r="B867" s="14" t="s">
+        <v>1834</v>
+      </c>
+      <c r="C867" s="14" t="s">
+        <v>562</v>
+      </c>
+      <c r="D867" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="E867" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F867" s="14" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="868" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A868" s="11">
+        <v>867</v>
+      </c>
+      <c r="B868" s="12" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C868" s="12" t="s">
+        <v>664</v>
+      </c>
+      <c r="D868" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E868" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F868" s="12" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="869" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A869" s="13">
+        <v>868</v>
+      </c>
+      <c r="B869" s="14" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C869" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="D869" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E869" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F869" s="14" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="870" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A870" s="11">
+        <v>869</v>
+      </c>
+      <c r="B870" s="12" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C870" s="12" t="s">
+        <v>780</v>
+      </c>
+      <c r="D870" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E870" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F870" s="12" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="871" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A871" s="13">
+        <v>870</v>
+      </c>
+      <c r="B871" s="14" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C871" s="14" t="s">
+        <v>943</v>
+      </c>
+      <c r="D871" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="E871" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F871" s="14" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="872" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A872" s="11">
+        <v>871</v>
+      </c>
+      <c r="B872" s="12" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C872" s="12" t="s">
+        <v>954</v>
+      </c>
+      <c r="D872" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="E872" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F872" s="12" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="873" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A873" s="13">
+        <v>872</v>
+      </c>
+      <c r="B873" s="14" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C873" s="14" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D873" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E873" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F873" s="14" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="874" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A874" s="11">
+        <v>873</v>
+      </c>
+      <c r="B874" s="12" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C874" s="12" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D874" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E874" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F874" s="12" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="875" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A875" s="13">
+        <v>874</v>
+      </c>
+      <c r="B875" s="14" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C875" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D875" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E875" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F875" s="14" t="s">
+        <v>1852</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/policy-tracker.xlsx
+++ b/reports/policy-tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4376" uniqueCount="1853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4446" uniqueCount="1881">
   <si>
     <t>Run #</t>
   </si>
@@ -5573,6 +5573,90 @@
   </si>
   <si>
     <t>15/09/2026, 13:44:34</t>
+  </si>
+  <si>
+    <t>CP-NI-081099258</t>
+  </si>
+  <si>
+    <t>15/09/2026, 14:15:19</t>
+  </si>
+  <si>
+    <t>CP-NI-081100258</t>
+  </si>
+  <si>
+    <t>15/09/2026, 14:16:17</t>
+  </si>
+  <si>
+    <t>CP-SC-081101258</t>
+  </si>
+  <si>
+    <t>15/09/2026, 14:17:11</t>
+  </si>
+  <si>
+    <t>CP-SC-081102258</t>
+  </si>
+  <si>
+    <t>15/09/2026, 14:18:06</t>
+  </si>
+  <si>
+    <t>DA-MLI-081103258</t>
+  </si>
+  <si>
+    <t>15/09/2026, 14:19:01</t>
+  </si>
+  <si>
+    <t>DA-MLI-081105258</t>
+  </si>
+  <si>
+    <t>15/09/2026, 14:19:47</t>
+  </si>
+  <si>
+    <t>DA-NI-081106258</t>
+  </si>
+  <si>
+    <t>15/09/2026, 14:20:49</t>
+  </si>
+  <si>
+    <t>CP-MLI-081108258</t>
+  </si>
+  <si>
+    <t>15/09/2026, 14:21:43</t>
+  </si>
+  <si>
+    <t>DA-MLI-081109258</t>
+  </si>
+  <si>
+    <t>15/09/2026, 14:22:58</t>
+  </si>
+  <si>
+    <t>DA-MLI-081112258</t>
+  </si>
+  <si>
+    <t>15/09/2026, 14:25:13</t>
+  </si>
+  <si>
+    <t>DA-MLI-081114258</t>
+  </si>
+  <si>
+    <t>15/09/2026, 14:29:55</t>
+  </si>
+  <si>
+    <t>DA-MLI-081117258</t>
+  </si>
+  <si>
+    <t>15/09/2026, 14:33:19</t>
+  </si>
+  <si>
+    <t>DA-MLI-081133258</t>
+  </si>
+  <si>
+    <t>15/09/2026, 14:41:58</t>
+  </si>
+  <si>
+    <t>DA-MLI-081153258</t>
+  </si>
+  <si>
+    <t>15/09/2026, 14:48:53</t>
   </si>
 </sst>
 </file>
@@ -6046,7 +6130,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F875"/>
+  <dimension ref="A1:F889"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -23557,6 +23641,286 @@
         <v>1852</v>
       </c>
     </row>
+    <row r="876" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A876" s="11">
+        <v>875</v>
+      </c>
+      <c r="B876" s="12" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C876" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D876" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="E876" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F876" s="12" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="877" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A877" s="13">
+        <v>876</v>
+      </c>
+      <c r="B877" s="14" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C877" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="D877" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="E877" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F877" s="14" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="878" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A878" s="11">
+        <v>877</v>
+      </c>
+      <c r="B878" s="12" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C878" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D878" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E878" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F878" s="12" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="879" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A879" s="13">
+        <v>878</v>
+      </c>
+      <c r="B879" s="14" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C879" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D879" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="E879" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F879" s="14" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="880" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A880" s="11">
+        <v>879</v>
+      </c>
+      <c r="B880" s="12" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C880" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="D880" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E880" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F880" s="12" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="881" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A881" s="13">
+        <v>880</v>
+      </c>
+      <c r="B881" s="14" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C881" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D881" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E881" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F881" s="14" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="882" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A882" s="11">
+        <v>881</v>
+      </c>
+      <c r="B882" s="12" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C882" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="D882" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E882" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F882" s="12" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="883" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A883" s="13">
+        <v>882</v>
+      </c>
+      <c r="B883" s="14" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C883" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="D883" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E883" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F883" s="14" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="884" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A884" s="11">
+        <v>883</v>
+      </c>
+      <c r="B884" s="12" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C884" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D884" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E884" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F884" s="12" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="885" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A885" s="13">
+        <v>884</v>
+      </c>
+      <c r="B885" s="14" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C885" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="D885" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E885" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F885" s="14" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="886" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A886" s="11">
+        <v>885</v>
+      </c>
+      <c r="B886" s="12" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C886" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="D886" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E886" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F886" s="12" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="887" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A887" s="13">
+        <v>886</v>
+      </c>
+      <c r="B887" s="14" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C887" s="14" t="s">
+        <v>534</v>
+      </c>
+      <c r="D887" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E887" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F887" s="14" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="888" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A888" s="11">
+        <v>887</v>
+      </c>
+      <c r="B888" s="12" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C888" s="12" t="s">
+        <v>780</v>
+      </c>
+      <c r="D888" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E888" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F888" s="12" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="889" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A889" s="13">
+        <v>888</v>
+      </c>
+      <c r="B889" s="14" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C889" s="14" t="s">
+        <v>780</v>
+      </c>
+      <c r="D889" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E889" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F889" s="14" t="s">
+        <v>1880</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/policy-tracker.xlsx
+++ b/reports/policy-tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4446" uniqueCount="1881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4581" uniqueCount="1949">
   <si>
     <t>Run #</t>
   </si>
@@ -5657,6 +5657,210 @@
   </si>
   <si>
     <t>15/09/2026, 14:48:53</t>
+  </si>
+  <si>
+    <t>DA-MLI-082859260</t>
+  </si>
+  <si>
+    <t>TC_REG_CLAIMS_BROKER_TO_OPEN_CLAIM_STATUS_CHANGE | Create broker policy, create claim, and complete Open Claim status</t>
+  </si>
+  <si>
+    <t>17/09/2026, 13:31:56</t>
+  </si>
+  <si>
+    <t>DA-MLI-082860260</t>
+  </si>
+  <si>
+    <t>TC_REG_CLAIMS_BROKER_TO_OPEN_CLAIM_STATUS_CHANGE | Create broker submission, open policy via Risk ID, create claim, and complete Open Circumstance status</t>
+  </si>
+  <si>
+    <t>17/09/2026, 13:38:13</t>
+  </si>
+  <si>
+    <t>DA-MLI-082861260</t>
+  </si>
+  <si>
+    <t>17/09/2026, 13:43:33</t>
+  </si>
+  <si>
+    <t>DA-MLI-082862260</t>
+  </si>
+  <si>
+    <t>TC_REG_034 | Create Claim on a live policy, fill claim info, and complete Open Circumstance status</t>
+  </si>
+  <si>
+    <t>17/09/2026, 13:49:39</t>
+  </si>
+  <si>
+    <t>DA-MLI-082863260</t>
+  </si>
+  <si>
+    <t>17/09/2026, 13:54:40</t>
+  </si>
+  <si>
+    <t>DA-MLI-082864260</t>
+  </si>
+  <si>
+    <t>17/09/2026, 13:59:20</t>
+  </si>
+  <si>
+    <t>DA-MLI-082865260</t>
+  </si>
+  <si>
+    <t>17/09/2026, 14:07:57</t>
+  </si>
+  <si>
+    <t>DA-MLI-082866260</t>
+  </si>
+  <si>
+    <t>17/09/2026, 14:12:38</t>
+  </si>
+  <si>
+    <t>DA-MLI-082867260</t>
+  </si>
+  <si>
+    <t>TC_REG_034 | Create Claim on a live policy and complete all claim path statuses</t>
+  </si>
+  <si>
+    <t>17/09/2026, 14:18:45</t>
+  </si>
+  <si>
+    <t>DA-MLI-082868260</t>
+  </si>
+  <si>
+    <t>17/09/2026, 14:23:04</t>
+  </si>
+  <si>
+    <t>DA-MLI-082870260</t>
+  </si>
+  <si>
+    <t>TC_REG_034 | Create Claim on a live policy and complete status: Open Circumstance</t>
+  </si>
+  <si>
+    <t>17/09/2026, 14:31:32</t>
+  </si>
+  <si>
+    <t>DA-MLI-082871260</t>
+  </si>
+  <si>
+    <t>TC_REG_034 | Create Claim on a live policy and complete status: Open Claim</t>
+  </si>
+  <si>
+    <t>17/09/2026, 14:34:20</t>
+  </si>
+  <si>
+    <t>DA-MLI-082872260</t>
+  </si>
+  <si>
+    <t>TC_REG_034 | Create Claim on a live policy and complete status: Re-Opened Circumstance</t>
+  </si>
+  <si>
+    <t>17/09/2026, 14:38:00</t>
+  </si>
+  <si>
+    <t>DA-MLI-082873260</t>
+  </si>
+  <si>
+    <t>TC_REG_034 | Create Claim on a live policy and complete status: Re-Opened Claim</t>
+  </si>
+  <si>
+    <t>17/09/2026, 14:41:35</t>
+  </si>
+  <si>
+    <t>DA-MLI-082874260</t>
+  </si>
+  <si>
+    <t>TC_REG_034 | Create Claim on a live policy and complete status: Closed Circumstance</t>
+  </si>
+  <si>
+    <t>17/09/2026, 14:45:13</t>
+  </si>
+  <si>
+    <t>DA-MLI-082875260</t>
+  </si>
+  <si>
+    <t>17/09/2026, 14:50:21</t>
+  </si>
+  <si>
+    <t>DA-MLI-082876260</t>
+  </si>
+  <si>
+    <t>17/09/2026, 14:56:08</t>
+  </si>
+  <si>
+    <t>DA-MLI-082877260</t>
+  </si>
+  <si>
+    <t>17/09/2026, 15:08:01</t>
+  </si>
+  <si>
+    <t>DA-MLI-082878260</t>
+  </si>
+  <si>
+    <t>TC_REG_034 | Create Claim on a live policy, fill claim info, and complete Open Claim status</t>
+  </si>
+  <si>
+    <t>17/09/2026, 15:11:43</t>
+  </si>
+  <si>
+    <t>DA-MLI-082879260</t>
+  </si>
+  <si>
+    <t>TC_REG_034 | Create Claim on a live policy, fill claim info, and complete Re-Opened Circumstance status</t>
+  </si>
+  <si>
+    <t>17/09/2026, 15:15:13</t>
+  </si>
+  <si>
+    <t>DA-MLI-082880260</t>
+  </si>
+  <si>
+    <t>TC_REG_034 | Create Claim on a live policy, fill claim info, and complete Re-Opened Claim status</t>
+  </si>
+  <si>
+    <t>17/09/2026, 15:18:55</t>
+  </si>
+  <si>
+    <t>DA-MLI-082881260</t>
+  </si>
+  <si>
+    <t>TC_REG_034 | Create Claim on a live policy, fill claim info, and complete Closed Circumstance status</t>
+  </si>
+  <si>
+    <t>17/09/2026, 15:22:14</t>
+  </si>
+  <si>
+    <t>DA-MLI-082882260</t>
+  </si>
+  <si>
+    <t>TC_REG_034 | Create Claim on a live policy, fill claim info, and complete Closed Claim status</t>
+  </si>
+  <si>
+    <t>17/09/2026, 15:28:10</t>
+  </si>
+  <si>
+    <t>DA-MLI-082883260</t>
+  </si>
+  <si>
+    <t>17/09/2026, 15:34:17</t>
+  </si>
+  <si>
+    <t>DA-MLI-082884260</t>
+  </si>
+  <si>
+    <t>17/09/2026, 15:39:33</t>
+  </si>
+  <si>
+    <t>DA-MLI-082885260</t>
+  </si>
+  <si>
+    <t>17/09/2026, 15:47:04</t>
+  </si>
+  <si>
+    <t>DA-MLI-082886260</t>
+  </si>
+  <si>
+    <t>17/09/2026, 15:52:34</t>
   </si>
 </sst>
 </file>
@@ -6130,7 +6334,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F889"/>
+  <dimension ref="A1:F916"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -23921,6 +24125,546 @@
         <v>1880</v>
       </c>
     </row>
+    <row r="890" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A890" s="11">
+        <v>889</v>
+      </c>
+      <c r="B890" s="12" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C890" s="12" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D890" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E890" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F890" s="12" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="891" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A891" s="13">
+        <v>890</v>
+      </c>
+      <c r="B891" s="14" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C891" s="14" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D891" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E891" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F891" s="14" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="892" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A892" s="11">
+        <v>891</v>
+      </c>
+      <c r="B892" s="12" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C892" s="12" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D892" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E892" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F892" s="12" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="893" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A893" s="13">
+        <v>892</v>
+      </c>
+      <c r="B893" s="14" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C893" s="14" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D893" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E893" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F893" s="14" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="894" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A894" s="11">
+        <v>893</v>
+      </c>
+      <c r="B894" s="12" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C894" s="12" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D894" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E894" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F894" s="12" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="895" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A895" s="13">
+        <v>894</v>
+      </c>
+      <c r="B895" s="14" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C895" s="14" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D895" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E895" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F895" s="14" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="896" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A896" s="11">
+        <v>895</v>
+      </c>
+      <c r="B896" s="12" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C896" s="12" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D896" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E896" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F896" s="12" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="897" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A897" s="13">
+        <v>896</v>
+      </c>
+      <c r="B897" s="14" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C897" s="14" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D897" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E897" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F897" s="14" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="898" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A898" s="11">
+        <v>897</v>
+      </c>
+      <c r="B898" s="12" t="s">
+        <v>1900</v>
+      </c>
+      <c r="C898" s="12" t="s">
+        <v>1901</v>
+      </c>
+      <c r="D898" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E898" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F898" s="12" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="899" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A899" s="13">
+        <v>898</v>
+      </c>
+      <c r="B899" s="14" t="s">
+        <v>1903</v>
+      </c>
+      <c r="C899" s="14" t="s">
+        <v>1901</v>
+      </c>
+      <c r="D899" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E899" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F899" s="14" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="900" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A900" s="11">
+        <v>899</v>
+      </c>
+      <c r="B900" s="12" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C900" s="12" t="s">
+        <v>1906</v>
+      </c>
+      <c r="D900" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E900" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F900" s="12" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="901" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A901" s="13">
+        <v>900</v>
+      </c>
+      <c r="B901" s="14" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C901" s="14" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D901" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E901" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F901" s="14" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="902" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A902" s="11">
+        <v>901</v>
+      </c>
+      <c r="B902" s="12" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C902" s="12" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D902" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E902" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F902" s="12" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="903" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A903" s="13">
+        <v>902</v>
+      </c>
+      <c r="B903" s="14" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C903" s="14" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D903" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E903" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F903" s="14" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="904" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A904" s="11">
+        <v>903</v>
+      </c>
+      <c r="B904" s="12" t="s">
+        <v>1917</v>
+      </c>
+      <c r="C904" s="12" t="s">
+        <v>1918</v>
+      </c>
+      <c r="D904" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E904" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F904" s="12" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="905" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A905" s="13">
+        <v>904</v>
+      </c>
+      <c r="B905" s="14" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C905" s="14" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D905" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E905" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F905" s="14" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="906" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A906" s="11">
+        <v>905</v>
+      </c>
+      <c r="B906" s="12" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C906" s="12" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D906" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E906" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F906" s="12" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="907" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A907" s="13">
+        <v>906</v>
+      </c>
+      <c r="B907" s="14" t="s">
+        <v>1924</v>
+      </c>
+      <c r="C907" s="14" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D907" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E907" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F907" s="14" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="908" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A908" s="11">
+        <v>907</v>
+      </c>
+      <c r="B908" s="12" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C908" s="12" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D908" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E908" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F908" s="12" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="909" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A909" s="13">
+        <v>908</v>
+      </c>
+      <c r="B909" s="14" t="s">
+        <v>1929</v>
+      </c>
+      <c r="C909" s="14" t="s">
+        <v>1930</v>
+      </c>
+      <c r="D909" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E909" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F909" s="14" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="910" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A910" s="11">
+        <v>909</v>
+      </c>
+      <c r="B910" s="12" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C910" s="12" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D910" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E910" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F910" s="12" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="911" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A911" s="13">
+        <v>910</v>
+      </c>
+      <c r="B911" s="14" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C911" s="14" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D911" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E911" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F911" s="14" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="912" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A912" s="11">
+        <v>911</v>
+      </c>
+      <c r="B912" s="12" t="s">
+        <v>1938</v>
+      </c>
+      <c r="C912" s="12" t="s">
+        <v>1939</v>
+      </c>
+      <c r="D912" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E912" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F912" s="12" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="913" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A913" s="13">
+        <v>912</v>
+      </c>
+      <c r="B913" s="14" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C913" s="14" t="s">
+        <v>1939</v>
+      </c>
+      <c r="D913" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E913" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F913" s="14" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="914" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A914" s="11">
+        <v>913</v>
+      </c>
+      <c r="B914" s="12" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C914" s="12" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D914" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E914" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F914" s="12" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="915" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A915" s="13">
+        <v>914</v>
+      </c>
+      <c r="B915" s="14" t="s">
+        <v>1945</v>
+      </c>
+      <c r="C915" s="14" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D915" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E915" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F915" s="14" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="916" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A916" s="11">
+        <v>915</v>
+      </c>
+      <c r="B916" s="12" t="s">
+        <v>1947</v>
+      </c>
+      <c r="C916" s="12" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D916" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E916" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F916" s="12" t="s">
+        <v>1948</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/policy-tracker.xlsx
+++ b/reports/policy-tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4581" uniqueCount="1949">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4616" uniqueCount="1964">
   <si>
     <t>Run #</t>
   </si>
@@ -5861,6 +5861,51 @@
   </si>
   <si>
     <t>17/09/2026, 15:52:34</t>
+  </si>
+  <si>
+    <t>CP-MLI-751975261</t>
+  </si>
+  <si>
+    <t>UAT1</t>
+  </si>
+  <si>
+    <t>18/09/2026, 14:27:56</t>
+  </si>
+  <si>
+    <t>CP-MLI-751976261</t>
+  </si>
+  <si>
+    <t>18/09/2026, 14:31:47</t>
+  </si>
+  <si>
+    <t>CP-MLI-751977261</t>
+  </si>
+  <si>
+    <t>18/09/2026, 14:33:45</t>
+  </si>
+  <si>
+    <t>CP-MLI-751978261</t>
+  </si>
+  <si>
+    <t>18/09/2026, 14:34:31</t>
+  </si>
+  <si>
+    <t>CP-MLI-751979261</t>
+  </si>
+  <si>
+    <t>18/09/2026, 14:36:01</t>
+  </si>
+  <si>
+    <t>CP-MLI-751980261</t>
+  </si>
+  <si>
+    <t>18/09/2026, 14:36:52</t>
+  </si>
+  <si>
+    <t>CP-MLI-751982261</t>
+  </si>
+  <si>
+    <t>18/09/2026, 14:58:15</t>
   </si>
 </sst>
 </file>
@@ -6334,7 +6379,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F916"/>
+  <dimension ref="A1:F923"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -24665,6 +24710,146 @@
         <v>1948</v>
       </c>
     </row>
+    <row r="917" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A917" s="13">
+        <v>916</v>
+      </c>
+      <c r="B917" s="14" t="s">
+        <v>1949</v>
+      </c>
+      <c r="C917" s="14" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D917" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E917" s="14" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F917" s="14" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="918" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A918" s="11">
+        <v>917</v>
+      </c>
+      <c r="B918" s="12" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C918" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D918" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E918" s="12" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F918" s="12" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="919" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A919" s="13">
+        <v>918</v>
+      </c>
+      <c r="B919" s="14" t="s">
+        <v>1954</v>
+      </c>
+      <c r="C919" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D919" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E919" s="14" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F919" s="14" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="920" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A920" s="11">
+        <v>919</v>
+      </c>
+      <c r="B920" s="12" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C920" s="12" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D920" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E920" s="12" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F920" s="12" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="921" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A921" s="13">
+        <v>920</v>
+      </c>
+      <c r="B921" s="14" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C921" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D921" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E921" s="14" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F921" s="14" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="922" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A922" s="11">
+        <v>921</v>
+      </c>
+      <c r="B922" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="C922" s="12" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D922" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E922" s="12" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F922" s="12" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="923" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A923" s="13">
+        <v>922</v>
+      </c>
+      <c r="B923" s="14" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C923" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D923" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E923" s="14" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F923" s="14" t="s">
+        <v>1963</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/policy-tracker.xlsx
+++ b/reports/policy-tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4616" uniqueCount="1964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4626" uniqueCount="1968">
   <si>
     <t>Run #</t>
   </si>
@@ -5906,6 +5906,18 @@
   </si>
   <si>
     <t>18/09/2026, 14:58:15</t>
+  </si>
+  <si>
+    <t>DA-MLI-554739264</t>
+  </si>
+  <si>
+    <t>21/09/2026, 18:58:52</t>
+  </si>
+  <si>
+    <t>DA-MLI-752017264</t>
+  </si>
+  <si>
+    <t>21/09/2026, 19:41:15</t>
   </si>
 </sst>
 </file>
@@ -6379,7 +6391,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F923"/>
+  <dimension ref="A1:F925"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -24850,6 +24862,46 @@
         <v>1963</v>
       </c>
     </row>
+    <row r="924" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A924" s="11">
+        <v>923</v>
+      </c>
+      <c r="B924" s="12" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C924" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="D924" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E924" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F924" s="12" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="925" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A925" s="13">
+        <v>924</v>
+      </c>
+      <c r="B925" s="14" t="s">
+        <v>1966</v>
+      </c>
+      <c r="C925" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D925" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E925" s="14" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F925" s="14" t="s">
+        <v>1967</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/policy-tracker.xlsx
+++ b/reports/policy-tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4626" uniqueCount="1968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4771" uniqueCount="2027">
   <si>
     <t>Run #</t>
   </si>
@@ -5918,6 +5918,183 @@
   </si>
   <si>
     <t>21/09/2026, 19:41:15</t>
+  </si>
+  <si>
+    <t>CP-NI-083431265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 19:38:27</t>
+  </si>
+  <si>
+    <t>CP-NI-083432265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 19:39:29</t>
+  </si>
+  <si>
+    <t>CP-SC-083433265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 19:40:34</t>
+  </si>
+  <si>
+    <t>CP-SC-083434265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 19:41:39</t>
+  </si>
+  <si>
+    <t>DA-MLI-083435265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 19:42:31</t>
+  </si>
+  <si>
+    <t>DA-MLI-083436265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 19:43:16</t>
+  </si>
+  <si>
+    <t>DA-NI-083437265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 19:44:14</t>
+  </si>
+  <si>
+    <t>DA-NI-083468265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 19:45:00</t>
+  </si>
+  <si>
+    <t>DA-SC-083469265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 19:45:54</t>
+  </si>
+  <si>
+    <t>DA-SC-083470265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 19:46:48</t>
+  </si>
+  <si>
+    <t>DA-MLI-083473265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 19:47:32</t>
+  </si>
+  <si>
+    <t>CP-MLI-083476265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 19:48:36</t>
+  </si>
+  <si>
+    <t>CP-SC-083479265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 19:49:36</t>
+  </si>
+  <si>
+    <t>DA-MLI-083489265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 19:50:30</t>
+  </si>
+  <si>
+    <t>DA-MLI-083509265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 19:52:48</t>
+  </si>
+  <si>
+    <t>DA-MLI-083535265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 19:57:12</t>
+  </si>
+  <si>
+    <t>DA-MLI-083565265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 20:01:44</t>
+  </si>
+  <si>
+    <t>DA-MLI-083613265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 20:10:11</t>
+  </si>
+  <si>
+    <t>DA-MLI-083642265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 20:13:49</t>
+  </si>
+  <si>
+    <t>DA-MLI-083653265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 20:16:38</t>
+  </si>
+  <si>
+    <t>DA-MLI-631290265</t>
+  </si>
+  <si>
+    <t>CLAIMSQA</t>
+  </si>
+  <si>
+    <t>22/09/2026, 21:11:49</t>
+  </si>
+  <si>
+    <t>DA-MLI-631291265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 21:15:32</t>
+  </si>
+  <si>
+    <t>DA-MLI-631292265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 21:18:43</t>
+  </si>
+  <si>
+    <t>DA-MLI-084059265</t>
+  </si>
+  <si>
+    <t>22/09/2026, 21:23:36</t>
+  </si>
+  <si>
+    <t>DA-MLI-631302266</t>
+  </si>
+  <si>
+    <t>23/09/2026, 11:36:51</t>
+  </si>
+  <si>
+    <t>DA-MLI-085132266</t>
+  </si>
+  <si>
+    <t>23/09/2026, 11:39:52</t>
+  </si>
+  <si>
+    <t>DA-MLI-631303266</t>
+  </si>
+  <si>
+    <t>23/09/2026, 11:46:27</t>
+  </si>
+  <si>
+    <t>DA-MLI-631304266</t>
+  </si>
+  <si>
+    <t>23/09/2026, 11:50:01</t>
+  </si>
+  <si>
+    <t>DA-MLI-752059266</t>
+  </si>
+  <si>
+    <t>23/09/2026, 14:07:14</t>
   </si>
 </sst>
 </file>
@@ -6391,7 +6568,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F925"/>
+  <dimension ref="A1:F954"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -24902,6 +25079,586 @@
         <v>1967</v>
       </c>
     </row>
+    <row r="926" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A926" s="11">
+        <v>925</v>
+      </c>
+      <c r="B926" s="12" t="s">
+        <v>1968</v>
+      </c>
+      <c r="C926" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D926" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="E926" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F926" s="12" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="927" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A927" s="13">
+        <v>926</v>
+      </c>
+      <c r="B927" s="14" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C927" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="D927" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="E927" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F927" s="14" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="928" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A928" s="11">
+        <v>927</v>
+      </c>
+      <c r="B928" s="12" t="s">
+        <v>1972</v>
+      </c>
+      <c r="C928" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D928" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E928" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F928" s="12" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="929" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A929" s="13">
+        <v>928</v>
+      </c>
+      <c r="B929" s="14" t="s">
+        <v>1974</v>
+      </c>
+      <c r="C929" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D929" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="E929" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F929" s="14" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="930" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A930" s="11">
+        <v>929</v>
+      </c>
+      <c r="B930" s="12" t="s">
+        <v>1976</v>
+      </c>
+      <c r="C930" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="D930" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E930" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F930" s="12" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="931" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A931" s="13">
+        <v>930</v>
+      </c>
+      <c r="B931" s="14" t="s">
+        <v>1978</v>
+      </c>
+      <c r="C931" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="D931" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E931" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F931" s="14" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="932" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A932" s="11">
+        <v>931</v>
+      </c>
+      <c r="B932" s="12" t="s">
+        <v>1980</v>
+      </c>
+      <c r="C932" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="D932" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E932" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F932" s="12" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="933" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A933" s="13">
+        <v>932</v>
+      </c>
+      <c r="B933" s="14" t="s">
+        <v>1982</v>
+      </c>
+      <c r="C933" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D933" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E933" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F933" s="14" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="934" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A934" s="11">
+        <v>933</v>
+      </c>
+      <c r="B934" s="12" t="s">
+        <v>1984</v>
+      </c>
+      <c r="C934" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="D934" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="E934" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F934" s="12" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="935" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A935" s="13">
+        <v>934</v>
+      </c>
+      <c r="B935" s="14" t="s">
+        <v>1986</v>
+      </c>
+      <c r="C935" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="D935" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="E935" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F935" s="14" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="936" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A936" s="11">
+        <v>935</v>
+      </c>
+      <c r="B936" s="12" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C936" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="D936" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E936" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F936" s="12" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="937" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A937" s="13">
+        <v>936</v>
+      </c>
+      <c r="B937" s="14" t="s">
+        <v>1990</v>
+      </c>
+      <c r="C937" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="D937" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E937" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F937" s="14" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="938" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A938" s="11">
+        <v>937</v>
+      </c>
+      <c r="B938" s="12" t="s">
+        <v>1992</v>
+      </c>
+      <c r="C938" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="D938" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E938" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F938" s="12" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="939" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A939" s="13">
+        <v>938</v>
+      </c>
+      <c r="B939" s="14" t="s">
+        <v>1994</v>
+      </c>
+      <c r="C939" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D939" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E939" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F939" s="14" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="940" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A940" s="11">
+        <v>939</v>
+      </c>
+      <c r="B940" s="12" t="s">
+        <v>1996</v>
+      </c>
+      <c r="C940" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D940" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E940" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F940" s="12" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="941" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A941" s="13">
+        <v>940</v>
+      </c>
+      <c r="B941" s="14" t="s">
+        <v>1998</v>
+      </c>
+      <c r="C941" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="D941" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E941" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F941" s="14" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="942" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A942" s="11">
+        <v>941</v>
+      </c>
+      <c r="B942" s="12" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C942" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="D942" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E942" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F942" s="12" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="943" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A943" s="13">
+        <v>942</v>
+      </c>
+      <c r="B943" s="14" t="s">
+        <v>2002</v>
+      </c>
+      <c r="C943" s="14" t="s">
+        <v>508</v>
+      </c>
+      <c r="D943" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E943" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F943" s="14" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="944" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A944" s="11">
+        <v>943</v>
+      </c>
+      <c r="B944" s="12" t="s">
+        <v>2004</v>
+      </c>
+      <c r="C944" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="D944" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E944" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F944" s="12" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="945" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A945" s="13">
+        <v>944</v>
+      </c>
+      <c r="B945" s="14" t="s">
+        <v>2006</v>
+      </c>
+      <c r="C945" s="14" t="s">
+        <v>534</v>
+      </c>
+      <c r="D945" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E945" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F945" s="14" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="946" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A946" s="11">
+        <v>945</v>
+      </c>
+      <c r="B946" s="12" t="s">
+        <v>2008</v>
+      </c>
+      <c r="C946" s="12" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D946" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E946" s="12" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F946" s="12" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="947" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A947" s="13">
+        <v>946</v>
+      </c>
+      <c r="B947" s="14" t="s">
+        <v>2011</v>
+      </c>
+      <c r="C947" s="14" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D947" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E947" s="14" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F947" s="14" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="948" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A948" s="11">
+        <v>947</v>
+      </c>
+      <c r="B948" s="12" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C948" s="12" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D948" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E948" s="12" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F948" s="12" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="949" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A949" s="13">
+        <v>948</v>
+      </c>
+      <c r="B949" s="14" t="s">
+        <v>2015</v>
+      </c>
+      <c r="C949" s="14" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D949" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E949" s="14" t="s">
+        <v>1584</v>
+      </c>
+      <c r="F949" s="14" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="950" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A950" s="11">
+        <v>949</v>
+      </c>
+      <c r="B950" s="12" t="s">
+        <v>2017</v>
+      </c>
+      <c r="C950" s="12" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D950" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E950" s="12" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F950" s="12" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="951" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A951" s="13">
+        <v>950</v>
+      </c>
+      <c r="B951" s="14" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C951" s="14" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D951" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E951" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F951" s="14" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="952" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A952" s="11">
+        <v>951</v>
+      </c>
+      <c r="B952" s="12" t="s">
+        <v>2021</v>
+      </c>
+      <c r="C952" s="12" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D952" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E952" s="12" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F952" s="12" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="953" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A953" s="13">
+        <v>952</v>
+      </c>
+      <c r="B953" s="14" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C953" s="14" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D953" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E953" s="14" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F953" s="14" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="954" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A954" s="11">
+        <v>953</v>
+      </c>
+      <c r="B954" s="12" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C954" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="D954" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E954" s="12" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F954" s="12" t="s">
+        <v>2026</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/policy-tracker.xlsx
+++ b/reports/policy-tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4771" uniqueCount="2027">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4776" uniqueCount="2029">
   <si>
     <t>Run #</t>
   </si>
@@ -6095,6 +6095,12 @@
   </si>
   <si>
     <t>23/09/2026, 14:07:14</t>
+  </si>
+  <si>
+    <t>DA-MLI-752136267</t>
+  </si>
+  <si>
+    <t>24/09/2026, 19:43:57</t>
   </si>
 </sst>
 </file>
@@ -6568,7 +6574,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F954"/>
+  <dimension ref="A1:F955"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -25659,6 +25665,26 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="955" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A955" s="13">
+        <v>954</v>
+      </c>
+      <c r="B955" s="14" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C955" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D955" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E955" s="14" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F955" s="14" t="s">
+        <v>2028</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/policy-tracker.xlsx
+++ b/reports/policy-tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4776" uniqueCount="2029">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4906" uniqueCount="2085">
   <si>
     <t>Run #</t>
   </si>
@@ -6101,6 +6101,174 @@
   </si>
   <si>
     <t>24/09/2026, 19:43:57</t>
+  </si>
+  <si>
+    <t>DA-MLI-085260267</t>
+  </si>
+  <si>
+    <t>TC_REG_CLAIMS_E2E_CREATE_CLAIM_AND_POST_RESERVE | Create live policy, create claim, and post reserve</t>
+  </si>
+  <si>
+    <t>24/09/2026, 19:59:02</t>
+  </si>
+  <si>
+    <t>DA-MLI-085261267</t>
+  </si>
+  <si>
+    <t>24/09/2026, 20:06:17</t>
+  </si>
+  <si>
+    <t>DA-MLI-631316267</t>
+  </si>
+  <si>
+    <t>24/09/2026, 20:13:01</t>
+  </si>
+  <si>
+    <t>DA-MLI-631317267</t>
+  </si>
+  <si>
+    <t>TC_REG_034 | Create Claim on a live policy, complete Open Claim status, and post reserve</t>
+  </si>
+  <si>
+    <t>24/09/2026, 20:15:50</t>
+  </si>
+  <si>
+    <t>DA-MLI-085262267</t>
+  </si>
+  <si>
+    <t>24/09/2026, 20:23:37</t>
+  </si>
+  <si>
+    <t>DA-MLI-085263267</t>
+  </si>
+  <si>
+    <t>TC_REG_034 | Create Claim on a live policy, complete Open Claim status, refresh, and click New Reserve</t>
+  </si>
+  <si>
+    <t>24/09/2026, 20:27:23</t>
+  </si>
+  <si>
+    <t>DA-MLI-085264267</t>
+  </si>
+  <si>
+    <t>24/09/2026, 20:32:59</t>
+  </si>
+  <si>
+    <t>DA-MLI-085265267</t>
+  </si>
+  <si>
+    <t>24/09/2026, 20:40:23</t>
+  </si>
+  <si>
+    <t>DA-MLI-085266267</t>
+  </si>
+  <si>
+    <t>24/09/2026, 21:05:28</t>
+  </si>
+  <si>
+    <t>DA-MLI-085267267</t>
+  </si>
+  <si>
+    <t>24/09/2026, 21:13:22</t>
+  </si>
+  <si>
+    <t>DA-MLI-631319267</t>
+  </si>
+  <si>
+    <t>TC_REG_034 | Create Claim on a live policy, complete Open Claim status, and complete reserve flow</t>
+  </si>
+  <si>
+    <t>24/09/2026, 21:19:17</t>
+  </si>
+  <si>
+    <t>DA-MLI-631320267</t>
+  </si>
+  <si>
+    <t>24/09/2026, 21:25:08</t>
+  </si>
+  <si>
+    <t>DA-MLI-631321267</t>
+  </si>
+  <si>
+    <t>24/09/2026, 21:30:15</t>
+  </si>
+  <si>
+    <t>DA-MLI-752151268</t>
+  </si>
+  <si>
+    <t>25/09/2026, 13:37:59</t>
+  </si>
+  <si>
+    <t>CP-MLI-752152268</t>
+  </si>
+  <si>
+    <t>25/09/2026, 13:39:48</t>
+  </si>
+  <si>
+    <t>CP-SC-752155268</t>
+  </si>
+  <si>
+    <t>25/09/2026, 13:41:22</t>
+  </si>
+  <si>
+    <t>DA-MLI-752157268</t>
+  </si>
+  <si>
+    <t>25/09/2026, 13:42:29</t>
+  </si>
+  <si>
+    <t>DA-MLI-752160268</t>
+  </si>
+  <si>
+    <t>25/09/2026, 13:45:32</t>
+  </si>
+  <si>
+    <t>DA-MLI-752162268</t>
+  </si>
+  <si>
+    <t>25/09/2026, 13:48:31</t>
+  </si>
+  <si>
+    <t>DA-MLI-752168268</t>
+  </si>
+  <si>
+    <t>25/09/2026, 13:52:42</t>
+  </si>
+  <si>
+    <t>DA-MLI-752179268</t>
+  </si>
+  <si>
+    <t>25/09/2026, 13:58:58</t>
+  </si>
+  <si>
+    <t>CP-NI-752191268</t>
+  </si>
+  <si>
+    <t>25/09/2026, 14:07:10</t>
+  </si>
+  <si>
+    <t>DA-MLI-752439268</t>
+  </si>
+  <si>
+    <t>25/09/2026, 18:17:22</t>
+  </si>
+  <si>
+    <t>DA-MLI-752484268</t>
+  </si>
+  <si>
+    <t>25/09/2026, 18:28:31</t>
+  </si>
+  <si>
+    <t>DA-MLI-752498268</t>
+  </si>
+  <si>
+    <t>25/09/2026, 18:31:52</t>
+  </si>
+  <si>
+    <t>DA-MLI-752508268</t>
+  </si>
+  <si>
+    <t>25/09/2026, 18:34:00</t>
   </si>
 </sst>
 </file>
@@ -6574,7 +6742,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F955"/>
+  <dimension ref="A1:F981"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -25685,6 +25853,526 @@
         <v>2028</v>
       </c>
     </row>
+    <row r="956" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A956" s="11">
+        <v>955</v>
+      </c>
+      <c r="B956" s="12" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C956" s="12" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D956" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E956" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F956" s="12" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="957" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A957" s="13">
+        <v>956</v>
+      </c>
+      <c r="B957" s="14" t="s">
+        <v>2032</v>
+      </c>
+      <c r="C957" s="14" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D957" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E957" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F957" s="14" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="958" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A958" s="11">
+        <v>957</v>
+      </c>
+      <c r="B958" s="12" t="s">
+        <v>2034</v>
+      </c>
+      <c r="C958" s="12" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D958" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E958" s="12" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F958" s="12" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="959" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A959" s="13">
+        <v>958</v>
+      </c>
+      <c r="B959" s="14" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C959" s="14" t="s">
+        <v>2037</v>
+      </c>
+      <c r="D959" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E959" s="14" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F959" s="14" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="960" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A960" s="11">
+        <v>959</v>
+      </c>
+      <c r="B960" s="12" t="s">
+        <v>2039</v>
+      </c>
+      <c r="C960" s="12" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D960" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E960" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F960" s="12" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="961" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A961" s="13">
+        <v>960</v>
+      </c>
+      <c r="B961" s="14" t="s">
+        <v>2041</v>
+      </c>
+      <c r="C961" s="14" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D961" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E961" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F961" s="14" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="962" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A962" s="11">
+        <v>961</v>
+      </c>
+      <c r="B962" s="12" t="s">
+        <v>2044</v>
+      </c>
+      <c r="C962" s="12" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D962" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E962" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F962" s="12" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="963" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A963" s="13">
+        <v>962</v>
+      </c>
+      <c r="B963" s="14" t="s">
+        <v>2046</v>
+      </c>
+      <c r="C963" s="14" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D963" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E963" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F963" s="14" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="964" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A964" s="11">
+        <v>963</v>
+      </c>
+      <c r="B964" s="12" t="s">
+        <v>2048</v>
+      </c>
+      <c r="C964" s="12" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D964" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E964" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="F964" s="12" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="965" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A965" s="13">
+        <v>964</v>
+      </c>
+      <c r="B965" s="14" t="s">
+        <v>2050</v>
+      </c>
+      <c r="C965" s="14" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D965" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E965" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="F965" s="14" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="966" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A966" s="11">
+        <v>965</v>
+      </c>
+      <c r="B966" s="12" t="s">
+        <v>2052</v>
+      </c>
+      <c r="C966" s="12" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D966" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E966" s="12" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F966" s="12" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="967" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A967" s="13">
+        <v>966</v>
+      </c>
+      <c r="B967" s="14" t="s">
+        <v>2055</v>
+      </c>
+      <c r="C967" s="14" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D967" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E967" s="14" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F967" s="14" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="968" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A968" s="11">
+        <v>967</v>
+      </c>
+      <c r="B968" s="12" t="s">
+        <v>2057</v>
+      </c>
+      <c r="C968" s="12" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D968" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E968" s="12" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F968" s="12" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="969" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A969" s="13">
+        <v>968</v>
+      </c>
+      <c r="B969" s="14" t="s">
+        <v>2059</v>
+      </c>
+      <c r="C969" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="D969" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E969" s="14" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F969" s="14" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="970" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A970" s="11">
+        <v>969</v>
+      </c>
+      <c r="B970" s="12" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C970" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="D970" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E970" s="12" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F970" s="12" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="971" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A971" s="13">
+        <v>970</v>
+      </c>
+      <c r="B971" s="14" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C971" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="D971" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="E971" s="14" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F971" s="14" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="972" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A972" s="11">
+        <v>971</v>
+      </c>
+      <c r="B972" s="12" t="s">
+        <v>2065</v>
+      </c>
+      <c r="C972" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="D972" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E972" s="12" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F972" s="12" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="973" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A973" s="13">
+        <v>972</v>
+      </c>
+      <c r="B973" s="14" t="s">
+        <v>2067</v>
+      </c>
+      <c r="C973" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D973" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E973" s="14" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F973" s="14" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="974" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A974" s="11">
+        <v>973</v>
+      </c>
+      <c r="B974" s="12" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C974" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="D974" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E974" s="12" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F974" s="12" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="975" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A975" s="13">
+        <v>974</v>
+      </c>
+      <c r="B975" s="14" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C975" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D975" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E975" s="14" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F975" s="14" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="976" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A976" s="11">
+        <v>975</v>
+      </c>
+      <c r="B976" s="12" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C976" s="12" t="s">
+        <v>780</v>
+      </c>
+      <c r="D976" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E976" s="12" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F976" s="12" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="977" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A977" s="13">
+        <v>976</v>
+      </c>
+      <c r="B977" s="14" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C977" s="14" t="s">
+        <v>943</v>
+      </c>
+      <c r="D977" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="E977" s="14" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F977" s="14" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="978" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A978" s="11">
+        <v>977</v>
+      </c>
+      <c r="B978" s="12" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C978" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="D978" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E978" s="12" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F978" s="12" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="979" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A979" s="13">
+        <v>978</v>
+      </c>
+      <c r="B979" s="14" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C979" s="14" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D979" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E979" s="14" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F979" s="14" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="980" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A980" s="11">
+        <v>979</v>
+      </c>
+      <c r="B980" s="12" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C980" s="12" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D980" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E980" s="12" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F980" s="12" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="981" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A981" s="13">
+        <v>980</v>
+      </c>
+      <c r="B981" s="14" t="s">
+        <v>2083</v>
+      </c>
+      <c r="C981" s="14" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D981" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E981" s="14" t="s">
+        <v>1950</v>
+      </c>
+      <c r="F981" s="14" t="s">
+        <v>2084</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/policy-tracker.xlsx
+++ b/reports/policy-tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4906" uniqueCount="2085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4956" uniqueCount="2107">
   <si>
     <t>Run #</t>
   </si>
@@ -6269,6 +6269,72 @@
   </si>
   <si>
     <t>25/09/2026, 18:34:00</t>
+  </si>
+  <si>
+    <t>CP-MLI-631334268</t>
+  </si>
+  <si>
+    <t>25/09/2026, 19:44:08</t>
+  </si>
+  <si>
+    <t>CP-MLI-631335268</t>
+  </si>
+  <si>
+    <t>25/09/2026, 19:52:23</t>
+  </si>
+  <si>
+    <t>CP-MLI-631336268</t>
+  </si>
+  <si>
+    <t>25/09/2026, 20:01:58</t>
+  </si>
+  <si>
+    <t>CP-MLI-631337268</t>
+  </si>
+  <si>
+    <t>25/09/2026, 20:26:51</t>
+  </si>
+  <si>
+    <t>CP-MLI-556211271</t>
+  </si>
+  <si>
+    <t>Create commercial England and Wales policy with four products</t>
+  </si>
+  <si>
+    <t>28/09/2026, 14:02:24</t>
+  </si>
+  <si>
+    <t>CP-MLI-556215271</t>
+  </si>
+  <si>
+    <t>28/09/2026, 15:12:17</t>
+  </si>
+  <si>
+    <t>DA-MLI-556223271</t>
+  </si>
+  <si>
+    <t>Cancel policy from inception after creating a fresh live policy</t>
+  </si>
+  <si>
+    <t>28/09/2026, 15:49:32</t>
+  </si>
+  <si>
+    <t>DA-MLI-556225271</t>
+  </si>
+  <si>
+    <t>28/09/2026, 16:10:42</t>
+  </si>
+  <si>
+    <t>DA-MLI-631413271</t>
+  </si>
+  <si>
+    <t>28/09/2026, 16:43:27</t>
+  </si>
+  <si>
+    <t>DA-MLI-631414271</t>
+  </si>
+  <si>
+    <t>28/09/2026, 16:48:45</t>
   </si>
 </sst>
 </file>
@@ -6742,7 +6808,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F981"/>
+  <dimension ref="A1:F991"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -26373,6 +26439,206 @@
         <v>2084</v>
       </c>
     </row>
+    <row r="982" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A982" s="11">
+        <v>981</v>
+      </c>
+      <c r="B982" s="12" t="s">
+        <v>2085</v>
+      </c>
+      <c r="C982" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D982" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E982" s="12" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F982" s="12" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="983" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A983" s="13">
+        <v>982</v>
+      </c>
+      <c r="B983" s="14" t="s">
+        <v>2087</v>
+      </c>
+      <c r="C983" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D983" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E983" s="14" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F983" s="14" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="984" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A984" s="11">
+        <v>983</v>
+      </c>
+      <c r="B984" s="12" t="s">
+        <v>2089</v>
+      </c>
+      <c r="C984" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D984" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E984" s="12" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F984" s="12" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="985" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A985" s="13">
+        <v>984</v>
+      </c>
+      <c r="B985" s="14" t="s">
+        <v>2091</v>
+      </c>
+      <c r="C985" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D985" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E985" s="14" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F985" s="14" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="986" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A986" s="11">
+        <v>985</v>
+      </c>
+      <c r="B986" s="12" t="s">
+        <v>2093</v>
+      </c>
+      <c r="C986" s="12" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D986" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E986" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F986" s="12" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="987" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A987" s="13">
+        <v>986</v>
+      </c>
+      <c r="B987" s="14" t="s">
+        <v>2096</v>
+      </c>
+      <c r="C987" s="14" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D987" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E987" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F987" s="14" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="988" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A988" s="11">
+        <v>987</v>
+      </c>
+      <c r="B988" s="12" t="s">
+        <v>2098</v>
+      </c>
+      <c r="C988" s="12" t="s">
+        <v>2099</v>
+      </c>
+      <c r="D988" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E988" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F988" s="12" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="989" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A989" s="13">
+        <v>988</v>
+      </c>
+      <c r="B989" s="14" t="s">
+        <v>2101</v>
+      </c>
+      <c r="C989" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="D989" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E989" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F989" s="14" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="990" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A990" s="11">
+        <v>989</v>
+      </c>
+      <c r="B990" s="12" t="s">
+        <v>2103</v>
+      </c>
+      <c r="C990" s="12" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D990" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E990" s="12" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F990" s="12" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="991" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A991" s="13">
+        <v>990</v>
+      </c>
+      <c r="B991" s="14" t="s">
+        <v>2105</v>
+      </c>
+      <c r="C991" s="14" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D991" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E991" s="14" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F991" s="14" t="s">
+        <v>2106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/policy-tracker.xlsx
+++ b/reports/policy-tracker.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4956" uniqueCount="2107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4961" uniqueCount="2110">
   <si>
     <t>Run #</t>
   </si>
@@ -6335,6 +6335,15 @@
   </si>
   <si>
     <t>28/09/2026, 16:48:45</t>
+  </si>
+  <si>
+    <t>DA-MLI-556256272</t>
+  </si>
+  <si>
+    <t>TC_REG_061 | Create Residential England &amp; Wales policy (end-to-end)</t>
+  </si>
+  <si>
+    <t>29/09/2026, 16:18:53</t>
   </si>
 </sst>
 </file>
@@ -6808,7 +6817,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F991"/>
+  <dimension ref="A1:F992"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -26639,6 +26648,26 @@
         <v>2106</v>
       </c>
     </row>
+    <row r="992" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A992" s="11">
+        <v>991</v>
+      </c>
+      <c r="B992" s="12" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C992" s="12" t="s">
+        <v>2108</v>
+      </c>
+      <c r="D992" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E992" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="F992" s="12" t="s">
+        <v>2109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
